--- a/Assets/StreamingAssets/digimon.xlsx
+++ b/Assets/StreamingAssets/digimon.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProject_Github\DGM_Project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A274408C-5430-4F42-A4BA-63F51DA9C6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801556EF-BF66-4E21-B04B-CA42715D1D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="5" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" firstSheet="2" activeTab="4" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
   </bookViews>
   <sheets>
     <sheet name="BabyStatus" sheetId="1" r:id="rId1"/>
     <sheet name="RookieStatus" sheetId="5" r:id="rId2"/>
     <sheet name="ChampionStatus" sheetId="6" r:id="rId3"/>
     <sheet name="EnemyStatus" sheetId="4" r:id="rId4"/>
-    <sheet name="GrowthType" sheetId="3" r:id="rId5"/>
-    <sheet name="EvoTree" sheetId="2" r:id="rId6"/>
+    <sheet name="VillageEast" sheetId="7" r:id="rId5"/>
+    <sheet name="Forest" sheetId="8" r:id="rId6"/>
+    <sheet name="Temple" sheetId="9" r:id="rId7"/>
+    <sheet name="GrowthType" sheetId="3" r:id="rId8"/>
+    <sheet name="EvoTree" sheetId="2" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="142">
   <si>
     <t>GrowthType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -562,6 +565,14 @@
   </si>
   <si>
     <t>Tyrannomon</t>
+  </si>
+  <si>
+    <t>EXP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2680,7 +2691,13 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A6">
-        <v>3005</v>
+        <v>3007</v>
+      </c>
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="D6" t="s">
         <v>93</v>
@@ -2688,7 +2705,18 @@
       <c r="E6" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J6">
         <v>1000</v>
       </c>
@@ -2710,7 +2738,13 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A7">
-        <v>3006</v>
+        <v>3008</v>
+      </c>
+      <c r="B7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="D7" t="s">
         <v>93</v>
@@ -2718,7 +2752,18 @@
       <c r="E7" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" t="s">
+        <v>75</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="J7">
         <v>1000</v>
       </c>
@@ -2740,13 +2785,13 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A8">
-        <v>3007</v>
+        <v>3009</v>
       </c>
       <c r="B8" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D8" t="s">
         <v>93</v>
@@ -2755,16 +2800,16 @@
         <v>92</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J8">
         <v>1000</v>
@@ -2787,13 +2832,13 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A9">
-        <v>3008</v>
+        <v>3010</v>
       </c>
       <c r="B9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
         <v>93</v>
@@ -2802,16 +2847,16 @@
         <v>92</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J9">
         <v>1000</v>
@@ -2834,13 +2879,13 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A10">
-        <v>3009</v>
+        <v>3011</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
         <v>93</v>
@@ -2849,10 +2894,10 @@
         <v>92</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
         <v>76</v>
@@ -2881,13 +2926,13 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A11">
-        <v>3010</v>
+        <v>3012</v>
       </c>
       <c r="B11" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
         <v>93</v>
@@ -2896,10 +2941,10 @@
         <v>92</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H11" t="s">
         <v>74</v>
@@ -2928,13 +2973,13 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A12">
-        <v>3011</v>
+        <v>3013</v>
       </c>
       <c r="B12" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
         <v>93</v>
@@ -2949,10 +2994,10 @@
         <v>67</v>
       </c>
       <c r="H12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J12">
         <v>1000</v>
@@ -2975,13 +3020,13 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A13">
-        <v>3012</v>
+        <v>3014</v>
       </c>
       <c r="B13" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
         <v>93</v>
@@ -2990,16 +3035,16 @@
         <v>92</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J13">
         <v>1000</v>
@@ -3022,13 +3067,13 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A14">
-        <v>3013</v>
+        <v>3015</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
         <v>93</v>
@@ -3043,10 +3088,10 @@
         <v>67</v>
       </c>
       <c r="H14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J14">
         <v>1000</v>
@@ -3069,13 +3114,13 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A15">
-        <v>3014</v>
+        <v>3016</v>
       </c>
       <c r="B15" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
         <v>93</v>
@@ -3090,10 +3135,10 @@
         <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="J15">
         <v>1000</v>
@@ -3116,13 +3161,13 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
       <c r="A16">
-        <v>3015</v>
+        <v>3017</v>
       </c>
       <c r="B16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D16" t="s">
         <v>93</v>
@@ -3131,10 +3176,10 @@
         <v>92</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" t="s">
         <v>75</v>
@@ -3161,104 +3206,10 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>3016</v>
-      </c>
-      <c r="B17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J17">
-        <v>1000</v>
-      </c>
-      <c r="K17">
-        <v>200</v>
-      </c>
-      <c r="L17">
-        <v>200</v>
-      </c>
-      <c r="M17">
-        <v>200</v>
-      </c>
-      <c r="N17">
-        <v>200</v>
-      </c>
-      <c r="O17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>3017</v>
-      </c>
-      <c r="B18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18">
-        <v>1000</v>
-      </c>
-      <c r="K18">
-        <v>200</v>
-      </c>
-      <c r="L18">
-        <v>200</v>
-      </c>
-      <c r="M18">
-        <v>200</v>
-      </c>
-      <c r="N18">
-        <v>200</v>
-      </c>
-      <c r="O18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.55000000000000004">
       <c r="H19" s="1"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.55000000000000004">
       <c r="H20" s="1"/>
     </row>
   </sheetData>
@@ -5457,6 +5408,776 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E6DA1-6182-4200-AD23-D3557DB026A8}">
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="15" max="15" width="16.0703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>5001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2">
+        <f>100+20*(P2-1)</f>
+        <v>240</v>
+      </c>
+      <c r="K2">
+        <f>20+5*(P2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="L2">
+        <f>20+5*(P2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="M2">
+        <f>20+5*(P2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="N2">
+        <f>20+5*(P2-1)</f>
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2">
+        <v>8</v>
+      </c>
+      <c r="Q2">
+        <f>1+2*(P2-1)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>5002</v>
+      </c>
+      <c r="B3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J11" si="0">100+20*(P3-1)</f>
+        <v>220</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K11" si="1">20+5*(P3-1)</f>
+        <v>50</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L11" si="2">20+5*(P3-1)</f>
+        <v>50</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M11" si="3">20+5*(P3-1)</f>
+        <v>50</v>
+      </c>
+      <c r="N3">
+        <v>20</v>
+      </c>
+      <c r="O3" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3">
+        <v>7</v>
+      </c>
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="4">1+2*(P3-1)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>5003</v>
+      </c>
+      <c r="B4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+      <c r="N4">
+        <v>20</v>
+      </c>
+      <c r="O4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4">
+        <v>6</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>5004</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="N5">
+        <v>20</v>
+      </c>
+      <c r="O5" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5">
+        <v>9</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>5005</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="3"/>
+        <v>40</v>
+      </c>
+      <c r="N6">
+        <v>20</v>
+      </c>
+      <c r="O6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>5006</v>
+      </c>
+      <c r="B7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="0"/>
+        <v>160</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="2"/>
+        <v>35</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="3"/>
+        <v>35</v>
+      </c>
+      <c r="N7">
+        <v>20</v>
+      </c>
+      <c r="O7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7">
+        <v>4</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>5007</v>
+      </c>
+      <c r="B8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="1"/>
+        <v>25</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="2"/>
+        <v>25</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="N8">
+        <v>20</v>
+      </c>
+      <c r="O8" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8">
+        <v>2</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>5008</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="2"/>
+        <v>20</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="N9">
+        <v>20</v>
+      </c>
+      <c r="O9" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>5009</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>260</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="3"/>
+        <v>60</v>
+      </c>
+      <c r="N10">
+        <v>20</v>
+      </c>
+      <c r="O10" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10">
+        <v>9</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="4"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>5010</v>
+      </c>
+      <c r="B11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>140</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>30</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="N11">
+        <v>20</v>
+      </c>
+      <c r="O11" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11">
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5230F0EE-6E0E-4F24-86B3-762891172ACA}">
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539D3BDA-0FE9-4E44-911C-7E21B9151C80}">
+  <dimension ref="A1:P1"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D12BA1-8205-47AD-8838-8518DB605E8F}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -5489,7 +6210,7 @@
         <v>10</v>
       </c>
       <c r="B2">
-        <f>C2*4</f>
+        <f>D2*4</f>
         <v>20</v>
       </c>
       <c r="C2">
@@ -5510,8 +6231,8 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B6" si="0">C3*4</f>
-        <v>32</v>
+        <f t="shared" ref="B3:B6" si="0">D3*4</f>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>8</v>
@@ -5532,7 +6253,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -5595,7 +6316,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9850558A-6B67-4F66-86DD-8F5D9DC7060A}">
   <dimension ref="A1:H47"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>

--- a/Assets/StreamingAssets/digimon.xlsx
+++ b/Assets/StreamingAssets/digimon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProject_Github\DGM_Project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801556EF-BF66-4E21-B04B-CA42715D1D94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB0E588-DC97-4F9F-9061-04B44AB2DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" firstSheet="2" activeTab="4" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
   </bookViews>

--- a/Assets/StreamingAssets/digimon.xlsx
+++ b/Assets/StreamingAssets/digimon.xlsx
@@ -8,20 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProject_Github\DGM_Project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB0E588-DC97-4F9F-9061-04B44AB2DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2282C8-4866-4E96-A53D-2BC43BE0BBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" firstSheet="2" activeTab="4" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="BabyStatus" sheetId="1" r:id="rId1"/>
-    <sheet name="RookieStatus" sheetId="5" r:id="rId2"/>
-    <sheet name="ChampionStatus" sheetId="6" r:id="rId3"/>
-    <sheet name="EnemyStatus" sheetId="4" r:id="rId4"/>
-    <sheet name="VillageEast" sheetId="7" r:id="rId5"/>
-    <sheet name="Forest" sheetId="8" r:id="rId6"/>
-    <sheet name="Temple" sheetId="9" r:id="rId7"/>
-    <sheet name="GrowthType" sheetId="3" r:id="rId8"/>
-    <sheet name="EvoTree" sheetId="2" r:id="rId9"/>
+    <sheet name="PlayerStatus" sheetId="10" r:id="rId1"/>
+    <sheet name="EnemyStatus" sheetId="4" r:id="rId2"/>
+    <sheet name="GrowthType" sheetId="3" r:id="rId3"/>
+    <sheet name="BabyStatus" sheetId="1" r:id="rId4"/>
+    <sheet name="RookieStatus" sheetId="5" r:id="rId5"/>
+    <sheet name="ChampionStatus" sheetId="6" r:id="rId6"/>
+    <sheet name="VillageEast" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="145">
   <si>
     <t>GrowthType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -518,10 +516,6 @@
     <t>Veemon</t>
   </si>
   <si>
-    <t>Next</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Greymon</t>
   </si>
   <si>
@@ -572,6 +566,22 @@
   </si>
   <si>
     <t>Level</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버드라몬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캅테리몬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Togemon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -596,12 +606,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -618,11 +646,29 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -958,6 +1004,5101 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A6B5FD-6714-48F7-A243-90EB8A61A1B2}">
+  <dimension ref="A1:P45"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="15" max="15" width="15.640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="2">
+        <v>150</v>
+      </c>
+      <c r="K2" s="2">
+        <v>30</v>
+      </c>
+      <c r="L2" s="2">
+        <v>30</v>
+      </c>
+      <c r="M2" s="2">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2">
+        <v>20</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="2">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2">
+        <v>1002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="2">
+        <v>150</v>
+      </c>
+      <c r="K3" s="2">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2">
+        <v>30</v>
+      </c>
+      <c r="M3" s="2">
+        <v>20</v>
+      </c>
+      <c r="N3" s="2">
+        <v>20</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="2">
+        <v>2002</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
+        <v>1003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="2">
+        <v>150</v>
+      </c>
+      <c r="K4" s="2">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2">
+        <v>20</v>
+      </c>
+      <c r="N4" s="2">
+        <v>20</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4" s="2">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>1004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="2">
+        <v>150</v>
+      </c>
+      <c r="K5" s="2">
+        <v>30</v>
+      </c>
+      <c r="L5" s="2">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="2">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>1005</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2">
+        <v>150</v>
+      </c>
+      <c r="K6" s="2">
+        <v>30</v>
+      </c>
+      <c r="L6" s="2">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2">
+        <v>20</v>
+      </c>
+      <c r="N6" s="2">
+        <v>20</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6" s="2">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>1006</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="2">
+        <v>150</v>
+      </c>
+      <c r="K7" s="2">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2">
+        <v>30</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20</v>
+      </c>
+      <c r="N7" s="2">
+        <v>20</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7" s="2">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2">
+        <v>1007</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="2">
+        <v>150</v>
+      </c>
+      <c r="K8" s="2">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2">
+        <v>30</v>
+      </c>
+      <c r="M8" s="2">
+        <v>20</v>
+      </c>
+      <c r="N8" s="2">
+        <v>20</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="2">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2">
+        <v>1008</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="2">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2">
+        <v>30</v>
+      </c>
+      <c r="L9" s="2">
+        <v>30</v>
+      </c>
+      <c r="M9" s="2">
+        <v>20</v>
+      </c>
+      <c r="N9" s="2">
+        <v>20</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="2">
+        <v>1009</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="2">
+        <v>150</v>
+      </c>
+      <c r="K10" s="2">
+        <v>30</v>
+      </c>
+      <c r="L10" s="2">
+        <v>30</v>
+      </c>
+      <c r="M10" s="2">
+        <v>20</v>
+      </c>
+      <c r="N10" s="2">
+        <v>20</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="2">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="2">
+        <v>1010</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="2">
+        <v>150</v>
+      </c>
+      <c r="K11" s="2">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2">
+        <v>30</v>
+      </c>
+      <c r="M11" s="2">
+        <v>20</v>
+      </c>
+      <c r="N11" s="2">
+        <v>20</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4">
+        <v>2001</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4">
+        <v>300</v>
+      </c>
+      <c r="K12" s="4">
+        <v>60</v>
+      </c>
+      <c r="L12" s="4">
+        <v>60</v>
+      </c>
+      <c r="M12" s="4">
+        <v>40</v>
+      </c>
+      <c r="N12" s="4">
+        <v>40</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="4">
+        <v>3001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4">
+        <v>2002</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="4">
+        <v>300</v>
+      </c>
+      <c r="K13" s="4">
+        <v>60</v>
+      </c>
+      <c r="L13" s="4">
+        <v>60</v>
+      </c>
+      <c r="M13" s="4">
+        <v>40</v>
+      </c>
+      <c r="N13" s="4">
+        <v>40</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P13" s="4">
+        <v>3002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4">
+        <v>2003</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="4">
+        <v>300</v>
+      </c>
+      <c r="K14" s="4">
+        <v>60</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60</v>
+      </c>
+      <c r="M14" s="4">
+        <v>40</v>
+      </c>
+      <c r="N14" s="4">
+        <v>40</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="4">
+        <v>3003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4">
+        <v>2004</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="4">
+        <v>300</v>
+      </c>
+      <c r="K15" s="4">
+        <v>60</v>
+      </c>
+      <c r="L15" s="4">
+        <v>60</v>
+      </c>
+      <c r="M15" s="4">
+        <v>40</v>
+      </c>
+      <c r="N15" s="4">
+        <v>40</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="4">
+        <v>3004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
+        <v>2005</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="4">
+        <v>300</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60</v>
+      </c>
+      <c r="L16" s="4">
+        <v>60</v>
+      </c>
+      <c r="M16" s="4">
+        <v>40</v>
+      </c>
+      <c r="N16" s="4">
+        <v>40</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4">
+        <v>2006</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="4">
+        <v>300</v>
+      </c>
+      <c r="K17" s="4">
+        <v>60</v>
+      </c>
+      <c r="L17" s="4">
+        <v>60</v>
+      </c>
+      <c r="M17" s="4">
+        <v>40</v>
+      </c>
+      <c r="N17" s="4">
+        <v>40</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
+        <v>2007</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="4">
+        <v>300</v>
+      </c>
+      <c r="K18" s="4">
+        <v>60</v>
+      </c>
+      <c r="L18" s="4">
+        <v>60</v>
+      </c>
+      <c r="M18" s="4">
+        <v>40</v>
+      </c>
+      <c r="N18" s="4">
+        <v>40</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="4">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4">
+        <v>2008</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="4">
+        <v>300</v>
+      </c>
+      <c r="K19" s="4">
+        <v>60</v>
+      </c>
+      <c r="L19" s="4">
+        <v>60</v>
+      </c>
+      <c r="M19" s="4">
+        <v>40</v>
+      </c>
+      <c r="N19" s="4">
+        <v>40</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="4">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
+        <v>2009</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="4">
+        <v>300</v>
+      </c>
+      <c r="K20" s="4">
+        <v>60</v>
+      </c>
+      <c r="L20" s="4">
+        <v>60</v>
+      </c>
+      <c r="M20" s="4">
+        <v>40</v>
+      </c>
+      <c r="N20" s="4">
+        <v>40</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="4">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>2010</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="4">
+        <v>300</v>
+      </c>
+      <c r="K21" s="4">
+        <v>60</v>
+      </c>
+      <c r="L21" s="4">
+        <v>60</v>
+      </c>
+      <c r="M21" s="4">
+        <v>40</v>
+      </c>
+      <c r="N21" s="4">
+        <v>40</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
+        <v>2011</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="4">
+        <v>300</v>
+      </c>
+      <c r="K22" s="4">
+        <v>60</v>
+      </c>
+      <c r="L22" s="4">
+        <v>60</v>
+      </c>
+      <c r="M22" s="4">
+        <v>40</v>
+      </c>
+      <c r="N22" s="4">
+        <v>40</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="4">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4">
+        <v>2012</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" s="4">
+        <v>300</v>
+      </c>
+      <c r="K23" s="4">
+        <v>60</v>
+      </c>
+      <c r="L23" s="4">
+        <v>60</v>
+      </c>
+      <c r="M23" s="4">
+        <v>40</v>
+      </c>
+      <c r="N23" s="4">
+        <v>40</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="4">
+        <v>3012</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4">
+        <v>2013</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" s="4">
+        <v>300</v>
+      </c>
+      <c r="K24" s="4">
+        <v>60</v>
+      </c>
+      <c r="L24" s="4">
+        <v>60</v>
+      </c>
+      <c r="M24" s="4">
+        <v>40</v>
+      </c>
+      <c r="N24" s="4">
+        <v>40</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="4">
+        <v>2014</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="4">
+        <v>300</v>
+      </c>
+      <c r="K25" s="4">
+        <v>60</v>
+      </c>
+      <c r="L25" s="4">
+        <v>60</v>
+      </c>
+      <c r="M25" s="4">
+        <v>40</v>
+      </c>
+      <c r="N25" s="4">
+        <v>40</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="4">
+        <v>3014</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="4">
+        <v>2015</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="4">
+        <v>300</v>
+      </c>
+      <c r="K26" s="4">
+        <v>60</v>
+      </c>
+      <c r="L26" s="4">
+        <v>60</v>
+      </c>
+      <c r="M26" s="4">
+        <v>40</v>
+      </c>
+      <c r="N26" s="4">
+        <v>40</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4">
+        <v>2016</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="4">
+        <v>300</v>
+      </c>
+      <c r="K27" s="4">
+        <v>60</v>
+      </c>
+      <c r="L27" s="4">
+        <v>60</v>
+      </c>
+      <c r="M27" s="4">
+        <v>40</v>
+      </c>
+      <c r="N27" s="4">
+        <v>40</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="4">
+        <v>2017</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="4">
+        <v>300</v>
+      </c>
+      <c r="K28" s="4">
+        <v>60</v>
+      </c>
+      <c r="L28" s="4">
+        <v>60</v>
+      </c>
+      <c r="M28" s="4">
+        <v>40</v>
+      </c>
+      <c r="N28" s="4">
+        <v>40</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P28" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="4">
+        <v>2018</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="4">
+        <v>300</v>
+      </c>
+      <c r="K29" s="4">
+        <v>60</v>
+      </c>
+      <c r="L29" s="4">
+        <v>60</v>
+      </c>
+      <c r="M29" s="4">
+        <v>40</v>
+      </c>
+      <c r="N29" s="4">
+        <v>40</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
+        <v>2019</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J30" s="4">
+        <v>300</v>
+      </c>
+      <c r="K30" s="4">
+        <v>60</v>
+      </c>
+      <c r="L30" s="4">
+        <v>60</v>
+      </c>
+      <c r="M30" s="4">
+        <v>40</v>
+      </c>
+      <c r="N30" s="4">
+        <v>40</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P30" s="4">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6">
+        <v>3001</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="6">
+        <v>500</v>
+      </c>
+      <c r="K31" s="6">
+        <v>100</v>
+      </c>
+      <c r="L31" s="6">
+        <v>100</v>
+      </c>
+      <c r="M31" s="6">
+        <v>70</v>
+      </c>
+      <c r="N31" s="6">
+        <v>70</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P31" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6">
+        <v>3002</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="6">
+        <v>500</v>
+      </c>
+      <c r="K32" s="6">
+        <v>100</v>
+      </c>
+      <c r="L32" s="6">
+        <v>100</v>
+      </c>
+      <c r="M32" s="6">
+        <v>70</v>
+      </c>
+      <c r="N32" s="6">
+        <v>70</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6">
+        <v>3003</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="6">
+        <v>500</v>
+      </c>
+      <c r="K33" s="6">
+        <v>100</v>
+      </c>
+      <c r="L33" s="6">
+        <v>100</v>
+      </c>
+      <c r="M33" s="6">
+        <v>70</v>
+      </c>
+      <c r="N33" s="6">
+        <v>70</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6">
+        <v>3004</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="6">
+        <v>500</v>
+      </c>
+      <c r="K34" s="6">
+        <v>100</v>
+      </c>
+      <c r="L34" s="6">
+        <v>100</v>
+      </c>
+      <c r="M34" s="6">
+        <v>70</v>
+      </c>
+      <c r="N34" s="6">
+        <v>70</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="6">
+        <v>3007</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J35" s="6">
+        <v>500</v>
+      </c>
+      <c r="K35" s="6">
+        <v>100</v>
+      </c>
+      <c r="L35" s="6">
+        <v>100</v>
+      </c>
+      <c r="M35" s="6">
+        <v>70</v>
+      </c>
+      <c r="N35" s="6">
+        <v>70</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6">
+        <v>3008</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="6">
+        <v>500</v>
+      </c>
+      <c r="K36" s="6">
+        <v>100</v>
+      </c>
+      <c r="L36" s="6">
+        <v>100</v>
+      </c>
+      <c r="M36" s="6">
+        <v>70</v>
+      </c>
+      <c r="N36" s="6">
+        <v>70</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P36" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="6">
+        <v>3009</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J37" s="6">
+        <v>500</v>
+      </c>
+      <c r="K37" s="6">
+        <v>100</v>
+      </c>
+      <c r="L37" s="6">
+        <v>100</v>
+      </c>
+      <c r="M37" s="6">
+        <v>70</v>
+      </c>
+      <c r="N37" s="6">
+        <v>70</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="6">
+        <v>3010</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J38" s="6">
+        <v>500</v>
+      </c>
+      <c r="K38" s="6">
+        <v>100</v>
+      </c>
+      <c r="L38" s="6">
+        <v>100</v>
+      </c>
+      <c r="M38" s="6">
+        <v>70</v>
+      </c>
+      <c r="N38" s="6">
+        <v>70</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="6">
+        <v>3011</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J39" s="6">
+        <v>500</v>
+      </c>
+      <c r="K39" s="6">
+        <v>100</v>
+      </c>
+      <c r="L39" s="6">
+        <v>100</v>
+      </c>
+      <c r="M39" s="6">
+        <v>70</v>
+      </c>
+      <c r="N39" s="6">
+        <v>70</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="6">
+        <v>3012</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40" s="6">
+        <v>500</v>
+      </c>
+      <c r="K40" s="6">
+        <v>100</v>
+      </c>
+      <c r="L40" s="6">
+        <v>100</v>
+      </c>
+      <c r="M40" s="6">
+        <v>70</v>
+      </c>
+      <c r="N40" s="6">
+        <v>70</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P40" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="6">
+        <v>3013</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J41" s="6">
+        <v>500</v>
+      </c>
+      <c r="K41" s="6">
+        <v>100</v>
+      </c>
+      <c r="L41" s="6">
+        <v>100</v>
+      </c>
+      <c r="M41" s="6">
+        <v>70</v>
+      </c>
+      <c r="N41" s="6">
+        <v>70</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P41" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="6">
+        <v>3014</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J42" s="6">
+        <v>500</v>
+      </c>
+      <c r="K42" s="6">
+        <v>100</v>
+      </c>
+      <c r="L42" s="6">
+        <v>100</v>
+      </c>
+      <c r="M42" s="6">
+        <v>70</v>
+      </c>
+      <c r="N42" s="6">
+        <v>70</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P42" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="6">
+        <v>3015</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J43" s="6">
+        <v>500</v>
+      </c>
+      <c r="K43" s="6">
+        <v>100</v>
+      </c>
+      <c r="L43" s="6">
+        <v>100</v>
+      </c>
+      <c r="M43" s="6">
+        <v>70</v>
+      </c>
+      <c r="N43" s="6">
+        <v>70</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P43" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="6">
+        <v>3016</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J44" s="6">
+        <v>500</v>
+      </c>
+      <c r="K44" s="6">
+        <v>100</v>
+      </c>
+      <c r="L44" s="6">
+        <v>100</v>
+      </c>
+      <c r="M44" s="6">
+        <v>70</v>
+      </c>
+      <c r="N44" s="6">
+        <v>70</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="6">
+        <v>3017</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J45" s="6">
+        <v>500</v>
+      </c>
+      <c r="K45" s="6">
+        <v>100</v>
+      </c>
+      <c r="L45" s="6">
+        <v>100</v>
+      </c>
+      <c r="M45" s="6">
+        <v>70</v>
+      </c>
+      <c r="N45" s="6">
+        <v>70</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15585912-2F3A-4585-9048-DC033A32B8BC}">
+  <dimension ref="A1:R47"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="15" max="15" width="15.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L1" t="s">
+        <v>33</v>
+      </c>
+      <c r="M1" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P1" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>140</v>
+      </c>
+      <c r="R1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J2" s="2">
+        <v>150</v>
+      </c>
+      <c r="K2" s="2">
+        <v>30</v>
+      </c>
+      <c r="L2" s="2">
+        <v>30</v>
+      </c>
+      <c r="M2" s="2">
+        <v>20</v>
+      </c>
+      <c r="N2" s="2">
+        <v>20</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>8</v>
+      </c>
+      <c r="R2" s="2">
+        <f>1+2*(Q2-1)</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2">
+        <v>5002</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="2">
+        <v>150</v>
+      </c>
+      <c r="K3" s="2">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2">
+        <v>30</v>
+      </c>
+      <c r="M3" s="2">
+        <v>20</v>
+      </c>
+      <c r="N3" s="2">
+        <v>20</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>7</v>
+      </c>
+      <c r="R3" s="2">
+        <f t="shared" ref="R3:R12" si="0">1+2*(Q3-1)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
+        <v>5003</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J4" s="2">
+        <v>150</v>
+      </c>
+      <c r="K4" s="2">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2">
+        <v>30</v>
+      </c>
+      <c r="M4" s="2">
+        <v>20</v>
+      </c>
+      <c r="N4" s="2">
+        <v>20</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>6</v>
+      </c>
+      <c r="R4" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>5004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="2">
+        <v>150</v>
+      </c>
+      <c r="K5" s="2">
+        <v>30</v>
+      </c>
+      <c r="L5" s="2">
+        <v>30</v>
+      </c>
+      <c r="M5" s="2">
+        <v>20</v>
+      </c>
+      <c r="N5" s="2">
+        <v>20</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>9</v>
+      </c>
+      <c r="R5" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>5005</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2">
+        <v>150</v>
+      </c>
+      <c r="K6" s="2">
+        <v>30</v>
+      </c>
+      <c r="L6" s="2">
+        <v>30</v>
+      </c>
+      <c r="M6" s="2">
+        <v>20</v>
+      </c>
+      <c r="N6" s="2">
+        <v>20</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>5</v>
+      </c>
+      <c r="R6" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>5006</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="2">
+        <v>150</v>
+      </c>
+      <c r="K7" s="2">
+        <v>30</v>
+      </c>
+      <c r="L7" s="2">
+        <v>30</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20</v>
+      </c>
+      <c r="N7" s="2">
+        <v>20</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>4</v>
+      </c>
+      <c r="R7" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2">
+        <v>5007</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="2">
+        <v>150</v>
+      </c>
+      <c r="K8" s="2">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2">
+        <v>30</v>
+      </c>
+      <c r="M8" s="2">
+        <v>20</v>
+      </c>
+      <c r="N8" s="2">
+        <v>20</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>2</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" s="2">
+        <v>5008</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="2">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2">
+        <v>30</v>
+      </c>
+      <c r="L9" s="2">
+        <v>30</v>
+      </c>
+      <c r="M9" s="2">
+        <v>20</v>
+      </c>
+      <c r="N9" s="2">
+        <v>20</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>1</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="2">
+        <v>5009</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="2">
+        <v>150</v>
+      </c>
+      <c r="K10" s="2">
+        <v>30</v>
+      </c>
+      <c r="L10" s="2">
+        <v>30</v>
+      </c>
+      <c r="M10" s="2">
+        <v>20</v>
+      </c>
+      <c r="N10" s="2">
+        <v>20</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P10" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>9</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="2">
+        <v>5010</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="2">
+        <v>150</v>
+      </c>
+      <c r="K11" s="2">
+        <v>30</v>
+      </c>
+      <c r="L11" s="2">
+        <v>30</v>
+      </c>
+      <c r="M11" s="2">
+        <v>20</v>
+      </c>
+      <c r="N11" s="2">
+        <v>20</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P11" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>3</v>
+      </c>
+      <c r="R11" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" s="4">
+        <v>6001</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J12" s="4">
+        <v>300</v>
+      </c>
+      <c r="K12" s="4">
+        <v>60</v>
+      </c>
+      <c r="L12" s="4">
+        <v>60</v>
+      </c>
+      <c r="M12" s="4">
+        <v>40</v>
+      </c>
+      <c r="N12" s="4">
+        <v>40</v>
+      </c>
+      <c r="O12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P12" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>11</v>
+      </c>
+      <c r="R12" s="4">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="4">
+        <v>6002</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="4">
+        <v>300</v>
+      </c>
+      <c r="K13" s="4">
+        <v>60</v>
+      </c>
+      <c r="L13" s="4">
+        <v>60</v>
+      </c>
+      <c r="M13" s="4">
+        <v>40</v>
+      </c>
+      <c r="N13" s="4">
+        <v>40</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P13" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>11</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" ref="R13:R47" si="1">1+2*(Q13-1)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="4">
+        <v>6003</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J14" s="4">
+        <v>300</v>
+      </c>
+      <c r="K14" s="4">
+        <v>60</v>
+      </c>
+      <c r="L14" s="4">
+        <v>60</v>
+      </c>
+      <c r="M14" s="4">
+        <v>40</v>
+      </c>
+      <c r="N14" s="4">
+        <v>40</v>
+      </c>
+      <c r="O14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P14" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>11</v>
+      </c>
+      <c r="R14" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="4">
+        <v>6004</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J15" s="4">
+        <v>300</v>
+      </c>
+      <c r="K15" s="4">
+        <v>60</v>
+      </c>
+      <c r="L15" s="4">
+        <v>60</v>
+      </c>
+      <c r="M15" s="4">
+        <v>40</v>
+      </c>
+      <c r="N15" s="4">
+        <v>40</v>
+      </c>
+      <c r="O15" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P15" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>11</v>
+      </c>
+      <c r="R15" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="4">
+        <v>6005</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="4">
+        <v>300</v>
+      </c>
+      <c r="K16" s="4">
+        <v>60</v>
+      </c>
+      <c r="L16" s="4">
+        <v>60</v>
+      </c>
+      <c r="M16" s="4">
+        <v>40</v>
+      </c>
+      <c r="N16" s="4">
+        <v>40</v>
+      </c>
+      <c r="O16" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P16" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>11</v>
+      </c>
+      <c r="R16" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="4">
+        <v>6006</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="4">
+        <v>300</v>
+      </c>
+      <c r="K17" s="4">
+        <v>60</v>
+      </c>
+      <c r="L17" s="4">
+        <v>60</v>
+      </c>
+      <c r="M17" s="4">
+        <v>40</v>
+      </c>
+      <c r="N17" s="4">
+        <v>40</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P17" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>11</v>
+      </c>
+      <c r="R17" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="4">
+        <v>6007</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J18" s="4">
+        <v>300</v>
+      </c>
+      <c r="K18" s="4">
+        <v>60</v>
+      </c>
+      <c r="L18" s="4">
+        <v>60</v>
+      </c>
+      <c r="M18" s="4">
+        <v>40</v>
+      </c>
+      <c r="N18" s="4">
+        <v>40</v>
+      </c>
+      <c r="O18" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P18" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>11</v>
+      </c>
+      <c r="R18" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="4">
+        <v>6008</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J19" s="4">
+        <v>300</v>
+      </c>
+      <c r="K19" s="4">
+        <v>60</v>
+      </c>
+      <c r="L19" s="4">
+        <v>60</v>
+      </c>
+      <c r="M19" s="4">
+        <v>40</v>
+      </c>
+      <c r="N19" s="4">
+        <v>40</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P19" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>11</v>
+      </c>
+      <c r="R19" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="4">
+        <v>6009</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J20" s="4">
+        <v>300</v>
+      </c>
+      <c r="K20" s="4">
+        <v>60</v>
+      </c>
+      <c r="L20" s="4">
+        <v>60</v>
+      </c>
+      <c r="M20" s="4">
+        <v>40</v>
+      </c>
+      <c r="N20" s="4">
+        <v>40</v>
+      </c>
+      <c r="O20" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P20" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q20" s="4">
+        <v>11</v>
+      </c>
+      <c r="R20" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="4">
+        <v>6010</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J21" s="4">
+        <v>300</v>
+      </c>
+      <c r="K21" s="4">
+        <v>60</v>
+      </c>
+      <c r="L21" s="4">
+        <v>60</v>
+      </c>
+      <c r="M21" s="4">
+        <v>40</v>
+      </c>
+      <c r="N21" s="4">
+        <v>40</v>
+      </c>
+      <c r="O21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P21" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q21" s="4">
+        <v>11</v>
+      </c>
+      <c r="R21" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="4">
+        <v>6011</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J22" s="4">
+        <v>300</v>
+      </c>
+      <c r="K22" s="4">
+        <v>60</v>
+      </c>
+      <c r="L22" s="4">
+        <v>60</v>
+      </c>
+      <c r="M22" s="4">
+        <v>40</v>
+      </c>
+      <c r="N22" s="4">
+        <v>40</v>
+      </c>
+      <c r="O22" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P22" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>11</v>
+      </c>
+      <c r="R22" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="4">
+        <v>6012</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J23" s="4">
+        <v>300</v>
+      </c>
+      <c r="K23" s="4">
+        <v>60</v>
+      </c>
+      <c r="L23" s="4">
+        <v>60</v>
+      </c>
+      <c r="M23" s="4">
+        <v>40</v>
+      </c>
+      <c r="N23" s="4">
+        <v>40</v>
+      </c>
+      <c r="O23" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P23" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>11</v>
+      </c>
+      <c r="R23" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="4">
+        <v>6013</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J24" s="4">
+        <v>300</v>
+      </c>
+      <c r="K24" s="4">
+        <v>60</v>
+      </c>
+      <c r="L24" s="4">
+        <v>60</v>
+      </c>
+      <c r="M24" s="4">
+        <v>40</v>
+      </c>
+      <c r="N24" s="4">
+        <v>40</v>
+      </c>
+      <c r="O24" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P24" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>11</v>
+      </c>
+      <c r="R24" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="4">
+        <v>6014</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J25" s="4">
+        <v>300</v>
+      </c>
+      <c r="K25" s="4">
+        <v>60</v>
+      </c>
+      <c r="L25" s="4">
+        <v>60</v>
+      </c>
+      <c r="M25" s="4">
+        <v>40</v>
+      </c>
+      <c r="N25" s="4">
+        <v>40</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P25" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>11</v>
+      </c>
+      <c r="R25" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="4">
+        <v>6015</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="J26" s="4">
+        <v>300</v>
+      </c>
+      <c r="K26" s="4">
+        <v>60</v>
+      </c>
+      <c r="L26" s="4">
+        <v>60</v>
+      </c>
+      <c r="M26" s="4">
+        <v>40</v>
+      </c>
+      <c r="N26" s="4">
+        <v>40</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P26" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>11</v>
+      </c>
+      <c r="R26" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="4">
+        <v>6016</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J27" s="4">
+        <v>300</v>
+      </c>
+      <c r="K27" s="4">
+        <v>60</v>
+      </c>
+      <c r="L27" s="4">
+        <v>60</v>
+      </c>
+      <c r="M27" s="4">
+        <v>40</v>
+      </c>
+      <c r="N27" s="4">
+        <v>40</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P27" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>11</v>
+      </c>
+      <c r="R27" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="4">
+        <v>6017</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="4">
+        <v>300</v>
+      </c>
+      <c r="K28" s="4">
+        <v>60</v>
+      </c>
+      <c r="L28" s="4">
+        <v>60</v>
+      </c>
+      <c r="M28" s="4">
+        <v>40</v>
+      </c>
+      <c r="N28" s="4">
+        <v>40</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P28" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>11</v>
+      </c>
+      <c r="R28" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="4">
+        <v>6018</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J29" s="4">
+        <v>300</v>
+      </c>
+      <c r="K29" s="4">
+        <v>60</v>
+      </c>
+      <c r="L29" s="4">
+        <v>60</v>
+      </c>
+      <c r="M29" s="4">
+        <v>40</v>
+      </c>
+      <c r="N29" s="4">
+        <v>40</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P29" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>11</v>
+      </c>
+      <c r="R29" s="4">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="4">
+        <v>6019</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J30" s="4">
+        <v>300</v>
+      </c>
+      <c r="K30" s="4">
+        <v>60</v>
+      </c>
+      <c r="L30" s="4">
+        <v>60</v>
+      </c>
+      <c r="M30" s="4">
+        <v>40</v>
+      </c>
+      <c r="N30" s="4">
+        <v>40</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="P30" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>19</v>
+      </c>
+      <c r="R30" s="4">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="6">
+        <v>7001</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J31" s="6">
+        <v>500</v>
+      </c>
+      <c r="K31" s="6">
+        <v>100</v>
+      </c>
+      <c r="L31" s="6">
+        <v>100</v>
+      </c>
+      <c r="M31" s="6">
+        <v>70</v>
+      </c>
+      <c r="N31" s="6">
+        <v>70</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P31" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>21</v>
+      </c>
+      <c r="R31" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="6">
+        <v>7002</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J32" s="6">
+        <v>500</v>
+      </c>
+      <c r="K32" s="6">
+        <v>100</v>
+      </c>
+      <c r="L32" s="6">
+        <v>100</v>
+      </c>
+      <c r="M32" s="6">
+        <v>70</v>
+      </c>
+      <c r="N32" s="6">
+        <v>70</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>21</v>
+      </c>
+      <c r="R32" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="6">
+        <v>7003</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J33" s="6">
+        <v>500</v>
+      </c>
+      <c r="K33" s="6">
+        <v>100</v>
+      </c>
+      <c r="L33" s="6">
+        <v>100</v>
+      </c>
+      <c r="M33" s="6">
+        <v>70</v>
+      </c>
+      <c r="N33" s="6">
+        <v>70</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>21</v>
+      </c>
+      <c r="R33" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="6">
+        <v>7004</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34" s="6">
+        <v>500</v>
+      </c>
+      <c r="K34" s="6">
+        <v>100</v>
+      </c>
+      <c r="L34" s="6">
+        <v>100</v>
+      </c>
+      <c r="M34" s="6">
+        <v>70</v>
+      </c>
+      <c r="N34" s="6">
+        <v>70</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>21</v>
+      </c>
+      <c r="R34" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="6">
+        <v>7005</v>
+      </c>
+      <c r="B35" s="6">
+        <v>1</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J35" s="6">
+        <v>500</v>
+      </c>
+      <c r="K35" s="6">
+        <v>100</v>
+      </c>
+      <c r="L35" s="6">
+        <v>100</v>
+      </c>
+      <c r="M35" s="6">
+        <v>70</v>
+      </c>
+      <c r="N35" s="6">
+        <v>70</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>21</v>
+      </c>
+      <c r="R35" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="6">
+        <v>7006</v>
+      </c>
+      <c r="B36" s="6">
+        <v>1</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J36" s="6">
+        <v>500</v>
+      </c>
+      <c r="K36" s="6">
+        <v>100</v>
+      </c>
+      <c r="L36" s="6">
+        <v>100</v>
+      </c>
+      <c r="M36" s="6">
+        <v>70</v>
+      </c>
+      <c r="N36" s="6">
+        <v>70</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P36" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>21</v>
+      </c>
+      <c r="R36" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="6">
+        <v>7007</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J37" s="6">
+        <v>500</v>
+      </c>
+      <c r="K37" s="6">
+        <v>100</v>
+      </c>
+      <c r="L37" s="6">
+        <v>100</v>
+      </c>
+      <c r="M37" s="6">
+        <v>70</v>
+      </c>
+      <c r="N37" s="6">
+        <v>70</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>21</v>
+      </c>
+      <c r="R37" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="6">
+        <v>7008</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I38" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J38" s="6">
+        <v>500</v>
+      </c>
+      <c r="K38" s="6">
+        <v>100</v>
+      </c>
+      <c r="L38" s="6">
+        <v>100</v>
+      </c>
+      <c r="M38" s="6">
+        <v>70</v>
+      </c>
+      <c r="N38" s="6">
+        <v>70</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>21</v>
+      </c>
+      <c r="R38" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="6">
+        <v>7009</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J39" s="6">
+        <v>500</v>
+      </c>
+      <c r="K39" s="6">
+        <v>100</v>
+      </c>
+      <c r="L39" s="6">
+        <v>100</v>
+      </c>
+      <c r="M39" s="6">
+        <v>70</v>
+      </c>
+      <c r="N39" s="6">
+        <v>70</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>21</v>
+      </c>
+      <c r="R39" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="6">
+        <v>7010</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J40" s="6">
+        <v>500</v>
+      </c>
+      <c r="K40" s="6">
+        <v>100</v>
+      </c>
+      <c r="L40" s="6">
+        <v>100</v>
+      </c>
+      <c r="M40" s="6">
+        <v>70</v>
+      </c>
+      <c r="N40" s="6">
+        <v>70</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P40" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>21</v>
+      </c>
+      <c r="R40" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" s="6">
+        <v>7011</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="J41" s="6">
+        <v>500</v>
+      </c>
+      <c r="K41" s="6">
+        <v>100</v>
+      </c>
+      <c r="L41" s="6">
+        <v>100</v>
+      </c>
+      <c r="M41" s="6">
+        <v>70</v>
+      </c>
+      <c r="N41" s="6">
+        <v>70</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P41" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>21</v>
+      </c>
+      <c r="R41" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" s="6">
+        <v>7012</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J42" s="6">
+        <v>500</v>
+      </c>
+      <c r="K42" s="6">
+        <v>100</v>
+      </c>
+      <c r="L42" s="6">
+        <v>100</v>
+      </c>
+      <c r="M42" s="6">
+        <v>70</v>
+      </c>
+      <c r="N42" s="6">
+        <v>70</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P42" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>21</v>
+      </c>
+      <c r="R42" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" s="6">
+        <v>7013</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J43" s="6">
+        <v>500</v>
+      </c>
+      <c r="K43" s="6">
+        <v>100</v>
+      </c>
+      <c r="L43" s="6">
+        <v>100</v>
+      </c>
+      <c r="M43" s="6">
+        <v>70</v>
+      </c>
+      <c r="N43" s="6">
+        <v>70</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P43" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>21</v>
+      </c>
+      <c r="R43" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="6">
+        <v>7014</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J44" s="6">
+        <v>500</v>
+      </c>
+      <c r="K44" s="6">
+        <v>100</v>
+      </c>
+      <c r="L44" s="6">
+        <v>100</v>
+      </c>
+      <c r="M44" s="6">
+        <v>70</v>
+      </c>
+      <c r="N44" s="6">
+        <v>70</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>21</v>
+      </c>
+      <c r="R44" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="6">
+        <v>7015</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J45" s="6">
+        <v>500</v>
+      </c>
+      <c r="K45" s="6">
+        <v>100</v>
+      </c>
+      <c r="L45" s="6">
+        <v>100</v>
+      </c>
+      <c r="M45" s="6">
+        <v>70</v>
+      </c>
+      <c r="N45" s="6">
+        <v>70</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>21</v>
+      </c>
+      <c r="R45" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="6">
+        <v>7016</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="J46" s="6">
+        <v>500</v>
+      </c>
+      <c r="K46" s="6">
+        <v>100</v>
+      </c>
+      <c r="L46" s="6">
+        <v>100</v>
+      </c>
+      <c r="M46" s="6">
+        <v>70</v>
+      </c>
+      <c r="N46" s="6">
+        <v>70</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P46" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>21</v>
+      </c>
+      <c r="R46" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="6">
+        <v>7017</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="I47" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J47" s="6">
+        <v>500</v>
+      </c>
+      <c r="K47" s="6">
+        <v>100</v>
+      </c>
+      <c r="L47" s="6">
+        <v>100</v>
+      </c>
+      <c r="M47" s="6">
+        <v>70</v>
+      </c>
+      <c r="N47" s="6">
+        <v>70</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="6">
+        <v>-1</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>21</v>
+      </c>
+      <c r="R47" s="6">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D12BA1-8205-47AD-8838-8518DB605E8F}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <f>D2*5</f>
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B6" si="0">D3*5</f>
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B63A90-5912-4059-8F6A-B0CD3C2852FE}">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -1491,7 +6632,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A09D80-B6F8-4637-B17F-FF997CFB0BAB}">
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -2446,7 +7587,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F4277A-D612-42DD-BD41-F36E114C3D17}">
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -2506,7 +7647,7 @@
         <v>3001</v>
       </c>
       <c r="B2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>79</v>
@@ -2553,7 +7694,7 @@
         <v>3002</v>
       </c>
       <c r="B3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>80</v>
@@ -2600,7 +7741,7 @@
         <v>3003</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>81</v>
@@ -2647,7 +7788,7 @@
         <v>3004</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>94</v>
@@ -2694,7 +7835,7 @@
         <v>3007</v>
       </c>
       <c r="B6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>90</v>
@@ -2741,7 +7882,7 @@
         <v>3008</v>
       </c>
       <c r="B7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>86</v>
@@ -2788,7 +7929,7 @@
         <v>3009</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>87</v>
@@ -2835,7 +7976,7 @@
         <v>3010</v>
       </c>
       <c r="B9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>88</v>
@@ -2882,7 +8023,7 @@
         <v>3011</v>
       </c>
       <c r="B10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>82</v>
@@ -2929,7 +8070,7 @@
         <v>3012</v>
       </c>
       <c r="B11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>83</v>
@@ -2976,7 +8117,7 @@
         <v>3013</v>
       </c>
       <c r="B12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>78</v>
@@ -3023,7 +8164,7 @@
         <v>3014</v>
       </c>
       <c r="B13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>85</v>
@@ -3070,7 +8211,7 @@
         <v>3015</v>
       </c>
       <c r="B14" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>89</v>
@@ -3117,7 +8258,7 @@
         <v>3016</v>
       </c>
       <c r="B15" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>91</v>
@@ -3164,7 +8305,7 @@
         <v>3017</v>
       </c>
       <c r="B16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>84</v>
@@ -3218,2196 +8359,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15585912-2F3A-4585-9048-DC033A32B8BC}">
-  <dimension ref="A1:O47"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="15" max="15" width="15.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>5001</v>
-      </c>
-      <c r="B2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
-      </c>
-      <c r="K2">
-        <v>20</v>
-      </c>
-      <c r="L2">
-        <v>20</v>
-      </c>
-      <c r="M2">
-        <v>20</v>
-      </c>
-      <c r="N2">
-        <v>20</v>
-      </c>
-      <c r="O2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>5002</v>
-      </c>
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3">
-        <v>100</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
-      </c>
-      <c r="M3">
-        <v>20</v>
-      </c>
-      <c r="N3">
-        <v>20</v>
-      </c>
-      <c r="O3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>5003</v>
-      </c>
-      <c r="B4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4">
-        <v>20</v>
-      </c>
-      <c r="L4">
-        <v>20</v>
-      </c>
-      <c r="M4">
-        <v>20</v>
-      </c>
-      <c r="N4">
-        <v>20</v>
-      </c>
-      <c r="O4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>5004</v>
-      </c>
-      <c r="B5" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-      <c r="K5">
-        <v>20</v>
-      </c>
-      <c r="L5">
-        <v>20</v>
-      </c>
-      <c r="M5">
-        <v>20</v>
-      </c>
-      <c r="N5">
-        <v>20</v>
-      </c>
-      <c r="O5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>5005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6">
-        <v>100</v>
-      </c>
-      <c r="K6">
-        <v>20</v>
-      </c>
-      <c r="L6">
-        <v>20</v>
-      </c>
-      <c r="M6">
-        <v>20</v>
-      </c>
-      <c r="N6">
-        <v>20</v>
-      </c>
-      <c r="O6" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>5006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7">
-        <v>100</v>
-      </c>
-      <c r="K7">
-        <v>20</v>
-      </c>
-      <c r="L7">
-        <v>20</v>
-      </c>
-      <c r="M7">
-        <v>20</v>
-      </c>
-      <c r="N7">
-        <v>20</v>
-      </c>
-      <c r="O7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>5007</v>
-      </c>
-      <c r="B8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8">
-        <v>100</v>
-      </c>
-      <c r="K8">
-        <v>20</v>
-      </c>
-      <c r="L8">
-        <v>20</v>
-      </c>
-      <c r="M8">
-        <v>20</v>
-      </c>
-      <c r="N8">
-        <v>20</v>
-      </c>
-      <c r="O8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>5008</v>
-      </c>
-      <c r="B9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9">
-        <v>100</v>
-      </c>
-      <c r="K9">
-        <v>20</v>
-      </c>
-      <c r="L9">
-        <v>20</v>
-      </c>
-      <c r="M9">
-        <v>20</v>
-      </c>
-      <c r="N9">
-        <v>20</v>
-      </c>
-      <c r="O9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>5009</v>
-      </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10">
-        <v>100</v>
-      </c>
-      <c r="K10">
-        <v>20</v>
-      </c>
-      <c r="L10">
-        <v>20</v>
-      </c>
-      <c r="M10">
-        <v>20</v>
-      </c>
-      <c r="N10">
-        <v>20</v>
-      </c>
-      <c r="O10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>5010</v>
-      </c>
-      <c r="B11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
-      <c r="K11">
-        <v>20</v>
-      </c>
-      <c r="L11">
-        <v>20</v>
-      </c>
-      <c r="M11">
-        <v>20</v>
-      </c>
-      <c r="N11">
-        <v>20</v>
-      </c>
-      <c r="O11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>6001</v>
-      </c>
-      <c r="B12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" t="s">
-        <v>56</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J12">
-        <v>300</v>
-      </c>
-      <c r="K12">
-        <v>100</v>
-      </c>
-      <c r="L12">
-        <v>100</v>
-      </c>
-      <c r="M12">
-        <v>100</v>
-      </c>
-      <c r="N12">
-        <v>100</v>
-      </c>
-      <c r="O12" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>6002</v>
-      </c>
-      <c r="B13" t="s">
-        <v>109</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J13">
-        <v>300</v>
-      </c>
-      <c r="K13">
-        <v>100</v>
-      </c>
-      <c r="L13">
-        <v>100</v>
-      </c>
-      <c r="M13">
-        <v>100</v>
-      </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>6003</v>
-      </c>
-      <c r="B14" t="s">
-        <v>118</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F14" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J14">
-        <v>300</v>
-      </c>
-      <c r="K14">
-        <v>100</v>
-      </c>
-      <c r="L14">
-        <v>100</v>
-      </c>
-      <c r="M14">
-        <v>100</v>
-      </c>
-      <c r="N14">
-        <v>100</v>
-      </c>
-      <c r="O14" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>6004</v>
-      </c>
-      <c r="B15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" t="s">
-        <v>56</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H15" t="s">
-        <v>76</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15">
-        <v>300</v>
-      </c>
-      <c r="K15">
-        <v>100</v>
-      </c>
-      <c r="L15">
-        <v>100</v>
-      </c>
-      <c r="M15">
-        <v>100</v>
-      </c>
-      <c r="N15">
-        <v>100</v>
-      </c>
-      <c r="O15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>6005</v>
-      </c>
-      <c r="B16" t="s">
-        <v>106</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" t="s">
-        <v>77</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16">
-        <v>300</v>
-      </c>
-      <c r="K16">
-        <v>100</v>
-      </c>
-      <c r="L16">
-        <v>100</v>
-      </c>
-      <c r="M16">
-        <v>100</v>
-      </c>
-      <c r="N16">
-        <v>100</v>
-      </c>
-      <c r="O16" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>6006</v>
-      </c>
-      <c r="B17" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" t="s">
-        <v>56</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H17" t="s">
-        <v>77</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17">
-        <v>300</v>
-      </c>
-      <c r="K17">
-        <v>100</v>
-      </c>
-      <c r="L17">
-        <v>100</v>
-      </c>
-      <c r="M17">
-        <v>100</v>
-      </c>
-      <c r="N17">
-        <v>100</v>
-      </c>
-      <c r="O17" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>6007</v>
-      </c>
-      <c r="B18" t="s">
-        <v>117</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18">
-        <v>300</v>
-      </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
-      <c r="N18">
-        <v>100</v>
-      </c>
-      <c r="O18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>6008</v>
-      </c>
-      <c r="B19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J19">
-        <v>300</v>
-      </c>
-      <c r="K19">
-        <v>100</v>
-      </c>
-      <c r="L19">
-        <v>100</v>
-      </c>
-      <c r="M19">
-        <v>100</v>
-      </c>
-      <c r="N19">
-        <v>100</v>
-      </c>
-      <c r="O19" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>6009</v>
-      </c>
-      <c r="B20" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" t="s">
-        <v>76</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20">
-        <v>300</v>
-      </c>
-      <c r="K20">
-        <v>100</v>
-      </c>
-      <c r="L20">
-        <v>100</v>
-      </c>
-      <c r="M20">
-        <v>100</v>
-      </c>
-      <c r="N20">
-        <v>100</v>
-      </c>
-      <c r="O20" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>6010</v>
-      </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" t="s">
-        <v>62</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H21" t="s">
-        <v>74</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J21">
-        <v>300</v>
-      </c>
-      <c r="K21">
-        <v>100</v>
-      </c>
-      <c r="L21">
-        <v>100</v>
-      </c>
-      <c r="M21">
-        <v>100</v>
-      </c>
-      <c r="N21">
-        <v>100</v>
-      </c>
-      <c r="O21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>6011</v>
-      </c>
-      <c r="B22" t="s">
-        <v>107</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F22" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H22" t="s">
-        <v>77</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J22">
-        <v>300</v>
-      </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>100</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>100</v>
-      </c>
-      <c r="O22" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>6012</v>
-      </c>
-      <c r="B23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" t="s">
-        <v>63</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H23" t="s">
-        <v>74</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J23">
-        <v>300</v>
-      </c>
-      <c r="K23">
-        <v>100</v>
-      </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
-      <c r="M23">
-        <v>100</v>
-      </c>
-      <c r="N23">
-        <v>100</v>
-      </c>
-      <c r="O23" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>6013</v>
-      </c>
-      <c r="B24" t="s">
-        <v>112</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D24" t="s">
-        <v>56</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F24" t="s">
-        <v>62</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H24" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J24">
-        <v>300</v>
-      </c>
-      <c r="K24">
-        <v>100</v>
-      </c>
-      <c r="L24">
-        <v>100</v>
-      </c>
-      <c r="M24">
-        <v>100</v>
-      </c>
-      <c r="N24">
-        <v>100</v>
-      </c>
-      <c r="O24" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>6014</v>
-      </c>
-      <c r="B25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F25" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J25">
-        <v>300</v>
-      </c>
-      <c r="K25">
-        <v>100</v>
-      </c>
-      <c r="L25">
-        <v>100</v>
-      </c>
-      <c r="M25">
-        <v>100</v>
-      </c>
-      <c r="N25">
-        <v>100</v>
-      </c>
-      <c r="O25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>6015</v>
-      </c>
-      <c r="B26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H26" t="s">
-        <v>75</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J26">
-        <v>300</v>
-      </c>
-      <c r="K26">
-        <v>100</v>
-      </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="M26">
-        <v>100</v>
-      </c>
-      <c r="N26">
-        <v>100</v>
-      </c>
-      <c r="O26" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>6016</v>
-      </c>
-      <c r="B27" t="s">
-        <v>115</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F27" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H27" t="s">
-        <v>76</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J27">
-        <v>300</v>
-      </c>
-      <c r="K27">
-        <v>100</v>
-      </c>
-      <c r="L27">
-        <v>100</v>
-      </c>
-      <c r="M27">
-        <v>100</v>
-      </c>
-      <c r="N27">
-        <v>100</v>
-      </c>
-      <c r="O27" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>6017</v>
-      </c>
-      <c r="B28" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H28" t="s">
-        <v>74</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28">
-        <v>300</v>
-      </c>
-      <c r="K28">
-        <v>100</v>
-      </c>
-      <c r="L28">
-        <v>100</v>
-      </c>
-      <c r="M28">
-        <v>100</v>
-      </c>
-      <c r="N28">
-        <v>100</v>
-      </c>
-      <c r="O28" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29">
-        <v>6018</v>
-      </c>
-      <c r="B29" t="s">
-        <v>108</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F29" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H29" t="s">
-        <v>76</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J29">
-        <v>300</v>
-      </c>
-      <c r="K29">
-        <v>100</v>
-      </c>
-      <c r="L29">
-        <v>100</v>
-      </c>
-      <c r="M29">
-        <v>100</v>
-      </c>
-      <c r="N29">
-        <v>100</v>
-      </c>
-      <c r="O29" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30">
-        <v>6019</v>
-      </c>
-      <c r="B30" t="s">
-        <v>116</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H30" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J30">
-        <v>300</v>
-      </c>
-      <c r="K30">
-        <v>100</v>
-      </c>
-      <c r="L30">
-        <v>100</v>
-      </c>
-      <c r="M30">
-        <v>100</v>
-      </c>
-      <c r="N30">
-        <v>100</v>
-      </c>
-      <c r="O30" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31">
-        <v>7001</v>
-      </c>
-      <c r="B31" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" t="s">
-        <v>74</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J31">
-        <v>1000</v>
-      </c>
-      <c r="K31">
-        <v>200</v>
-      </c>
-      <c r="L31">
-        <v>200</v>
-      </c>
-      <c r="M31">
-        <v>200</v>
-      </c>
-      <c r="N31">
-        <v>200</v>
-      </c>
-      <c r="O31" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
-        <v>7002</v>
-      </c>
-      <c r="B32" t="s">
-        <v>130</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" t="s">
-        <v>93</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H32" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32">
-        <v>1000</v>
-      </c>
-      <c r="K32">
-        <v>200</v>
-      </c>
-      <c r="L32">
-        <v>200</v>
-      </c>
-      <c r="M32">
-        <v>200</v>
-      </c>
-      <c r="N32">
-        <v>200</v>
-      </c>
-      <c r="O32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>7003</v>
-      </c>
-      <c r="B33" t="s">
-        <v>126</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>93</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F33" t="s">
-        <v>59</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" t="s">
-        <v>76</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J33">
-        <v>1000</v>
-      </c>
-      <c r="K33">
-        <v>200</v>
-      </c>
-      <c r="L33">
-        <v>200</v>
-      </c>
-      <c r="M33">
-        <v>200</v>
-      </c>
-      <c r="N33">
-        <v>200</v>
-      </c>
-      <c r="O33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
-        <v>7004</v>
-      </c>
-      <c r="B34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D34" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F34" t="s">
-        <v>59</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H34" t="s">
-        <v>76</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J34">
-        <v>1000</v>
-      </c>
-      <c r="K34">
-        <v>200</v>
-      </c>
-      <c r="L34">
-        <v>200</v>
-      </c>
-      <c r="M34">
-        <v>200</v>
-      </c>
-      <c r="N34">
-        <v>200</v>
-      </c>
-      <c r="O34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35">
-        <v>7005</v>
-      </c>
-      <c r="D35" t="s">
-        <v>93</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I35" s="1"/>
-      <c r="J35">
-        <v>1000</v>
-      </c>
-      <c r="K35">
-        <v>200</v>
-      </c>
-      <c r="L35">
-        <v>200</v>
-      </c>
-      <c r="M35">
-        <v>200</v>
-      </c>
-      <c r="N35">
-        <v>200</v>
-      </c>
-      <c r="O35" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36">
-        <v>7006</v>
-      </c>
-      <c r="D36" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I36" s="1"/>
-      <c r="J36">
-        <v>1000</v>
-      </c>
-      <c r="K36">
-        <v>200</v>
-      </c>
-      <c r="L36">
-        <v>200</v>
-      </c>
-      <c r="M36">
-        <v>200</v>
-      </c>
-      <c r="N36">
-        <v>200</v>
-      </c>
-      <c r="O36" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
-        <v>7007</v>
-      </c>
-      <c r="B37" t="s">
-        <v>138</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" t="s">
-        <v>93</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F37" t="s">
-        <v>60</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H37" t="s">
-        <v>75</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J37">
-        <v>1000</v>
-      </c>
-      <c r="K37">
-        <v>200</v>
-      </c>
-      <c r="L37">
-        <v>200</v>
-      </c>
-      <c r="M37">
-        <v>200</v>
-      </c>
-      <c r="N37">
-        <v>200</v>
-      </c>
-      <c r="O37" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
-        <v>7008</v>
-      </c>
-      <c r="B38" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" t="s">
-        <v>93</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" t="s">
-        <v>59</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H38" t="s">
-        <v>75</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J38">
-        <v>1000</v>
-      </c>
-      <c r="K38">
-        <v>200</v>
-      </c>
-      <c r="L38">
-        <v>200</v>
-      </c>
-      <c r="M38">
-        <v>200</v>
-      </c>
-      <c r="N38">
-        <v>200</v>
-      </c>
-      <c r="O38" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39">
-        <v>7009</v>
-      </c>
-      <c r="B39" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" t="s">
-        <v>93</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H39" t="s">
-        <v>76</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J39">
-        <v>1000</v>
-      </c>
-      <c r="K39">
-        <v>200</v>
-      </c>
-      <c r="L39">
-        <v>200</v>
-      </c>
-      <c r="M39">
-        <v>200</v>
-      </c>
-      <c r="N39">
-        <v>200</v>
-      </c>
-      <c r="O39" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
-        <v>7010</v>
-      </c>
-      <c r="B40" t="s">
-        <v>136</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" t="s">
-        <v>93</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F40" t="s">
-        <v>62</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" t="s">
-        <v>74</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J40">
-        <v>1000</v>
-      </c>
-      <c r="K40">
-        <v>200</v>
-      </c>
-      <c r="L40">
-        <v>200</v>
-      </c>
-      <c r="M40">
-        <v>200</v>
-      </c>
-      <c r="N40">
-        <v>200</v>
-      </c>
-      <c r="O40" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
-        <v>7011</v>
-      </c>
-      <c r="B41" t="s">
-        <v>128</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D41" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F41" t="s">
-        <v>62</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H41" t="s">
-        <v>76</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="J41">
-        <v>1000</v>
-      </c>
-      <c r="K41">
-        <v>200</v>
-      </c>
-      <c r="L41">
-        <v>200</v>
-      </c>
-      <c r="M41">
-        <v>200</v>
-      </c>
-      <c r="N41">
-        <v>200</v>
-      </c>
-      <c r="O41" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
-        <v>7012</v>
-      </c>
-      <c r="B42" t="s">
-        <v>129</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>93</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F42" t="s">
-        <v>63</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H42" t="s">
-        <v>74</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J42">
-        <v>1000</v>
-      </c>
-      <c r="K42">
-        <v>200</v>
-      </c>
-      <c r="L42">
-        <v>200</v>
-      </c>
-      <c r="M42">
-        <v>200</v>
-      </c>
-      <c r="N42">
-        <v>200</v>
-      </c>
-      <c r="O42" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
-        <v>7013</v>
-      </c>
-      <c r="B43" t="s">
-        <v>132</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D43" t="s">
-        <v>93</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" t="s">
-        <v>62</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H43" t="s">
-        <v>74</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J43">
-        <v>1000</v>
-      </c>
-      <c r="K43">
-        <v>200</v>
-      </c>
-      <c r="L43">
-        <v>200</v>
-      </c>
-      <c r="M43">
-        <v>200</v>
-      </c>
-      <c r="N43">
-        <v>200</v>
-      </c>
-      <c r="O43" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
-        <v>7014</v>
-      </c>
-      <c r="B44" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D44" t="s">
-        <v>93</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" t="s">
-        <v>60</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H44" t="s">
-        <v>77</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="J44">
-        <v>1000</v>
-      </c>
-      <c r="K44">
-        <v>200</v>
-      </c>
-      <c r="L44">
-        <v>200</v>
-      </c>
-      <c r="M44">
-        <v>200</v>
-      </c>
-      <c r="N44">
-        <v>200</v>
-      </c>
-      <c r="O44" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45">
-        <v>7015</v>
-      </c>
-      <c r="B45" t="s">
-        <v>137</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" t="s">
-        <v>75</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J45">
-        <v>1000</v>
-      </c>
-      <c r="K45">
-        <v>200</v>
-      </c>
-      <c r="L45">
-        <v>200</v>
-      </c>
-      <c r="M45">
-        <v>200</v>
-      </c>
-      <c r="N45">
-        <v>200</v>
-      </c>
-      <c r="O45" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46">
-        <v>7016</v>
-      </c>
-      <c r="B46" t="s">
-        <v>139</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D46" t="s">
-        <v>93</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F46" t="s">
-        <v>60</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H46" t="s">
-        <v>74</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="J46">
-        <v>1000</v>
-      </c>
-      <c r="K46">
-        <v>200</v>
-      </c>
-      <c r="L46">
-        <v>200</v>
-      </c>
-      <c r="M46">
-        <v>200</v>
-      </c>
-      <c r="N46">
-        <v>200</v>
-      </c>
-      <c r="O46" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47">
-        <v>7017</v>
-      </c>
-      <c r="B47" t="s">
-        <v>135</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D47" t="s">
-        <v>93</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F47" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H47" t="s">
-        <v>75</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J47">
-        <v>1000</v>
-      </c>
-      <c r="K47">
-        <v>200</v>
-      </c>
-      <c r="L47">
-        <v>200</v>
-      </c>
-      <c r="M47">
-        <v>200</v>
-      </c>
-      <c r="N47">
-        <v>200</v>
-      </c>
-      <c r="O47" t="s">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E6DA1-6182-4200-AD23-D3557DB026A8}">
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -5462,10 +8414,10 @@
         <v>0</v>
       </c>
       <c r="P1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -6048,698 +9000,6 @@
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5230F0EE-6E0E-4F24-86B3-762891172ACA}">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{539D3BDA-0FE9-4E44-911C-7E21B9151C80}">
-  <dimension ref="A1:P1"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L1" t="s">
-        <v>33</v>
-      </c>
-      <c r="M1" t="s">
-        <v>34</v>
-      </c>
-      <c r="N1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O1" t="s">
-        <v>0</v>
-      </c>
-      <c r="P1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47D12BA1-8205-47AD-8838-8518DB605E8F}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
-  <cols>
-    <col min="1" max="1" width="12.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2">
-        <f>D2*4</f>
-        <v>20</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>5</v>
-      </c>
-      <c r="F2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <f t="shared" ref="B3:B6" si="0">D3*4</f>
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5">
-        <v>9</v>
-      </c>
-      <c r="F5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>3</v>
-      </c>
-      <c r="E6">
-        <v>5</v>
-      </c>
-      <c r="F6">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9850558A-6B67-4F66-86DD-8F5D9DC7060A}">
-  <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2">
-        <v>1001</v>
-      </c>
-      <c r="B2">
-        <v>2001</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3">
-        <v>1002</v>
-      </c>
-      <c r="B3">
-        <v>2002</v>
-      </c>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4">
-        <v>1003</v>
-      </c>
-      <c r="B4">
-        <v>2003</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5">
-        <v>1004</v>
-      </c>
-      <c r="B5">
-        <v>2004</v>
-      </c>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6">
-        <v>1005</v>
-      </c>
-      <c r="B6">
-        <v>2005</v>
-      </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7">
-        <v>1006</v>
-      </c>
-      <c r="B7">
-        <v>2006</v>
-      </c>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8">
-        <v>1007</v>
-      </c>
-      <c r="B8">
-        <v>2007</v>
-      </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9">
-        <v>1008</v>
-      </c>
-      <c r="B9">
-        <v>2008</v>
-      </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10">
-        <v>1009</v>
-      </c>
-      <c r="B10">
-        <v>2009</v>
-      </c>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11">
-        <v>1010</v>
-      </c>
-      <c r="B11">
-        <v>2010</v>
-      </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12">
-        <v>2001</v>
-      </c>
-      <c r="B12">
-        <v>3001</v>
-      </c>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13">
-        <v>2002</v>
-      </c>
-      <c r="B13">
-        <v>3002</v>
-      </c>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A14">
-        <v>2003</v>
-      </c>
-      <c r="B14">
-        <v>3003</v>
-      </c>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15">
-        <v>2004</v>
-      </c>
-      <c r="B15">
-        <v>3004</v>
-      </c>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A16">
-        <v>2005</v>
-      </c>
-      <c r="B16">
-        <v>-1</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A17">
-        <v>2006</v>
-      </c>
-      <c r="B17">
-        <v>-1</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18">
-        <v>2007</v>
-      </c>
-      <c r="B18">
-        <v>3007</v>
-      </c>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19">
-        <v>2008</v>
-      </c>
-      <c r="B19">
-        <v>3008</v>
-      </c>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20">
-        <v>2009</v>
-      </c>
-      <c r="B20">
-        <v>3009</v>
-      </c>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21">
-        <v>2010</v>
-      </c>
-      <c r="B21">
-        <v>-1</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22">
-        <v>2011</v>
-      </c>
-      <c r="B22">
-        <v>3011</v>
-      </c>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23">
-        <v>2012</v>
-      </c>
-      <c r="B23">
-        <v>3012</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24">
-        <v>2013</v>
-      </c>
-      <c r="B24">
-        <v>3013</v>
-      </c>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25">
-        <v>2014</v>
-      </c>
-      <c r="B25">
-        <v>3014</v>
-      </c>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26">
-        <v>2015</v>
-      </c>
-      <c r="B26">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27">
-        <v>2016</v>
-      </c>
-      <c r="B27">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28">
-        <v>2017</v>
-      </c>
-      <c r="B28">
-        <v>-1</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29">
-        <v>2018</v>
-      </c>
-      <c r="B29">
-        <v>-1</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A30">
-        <v>2019</v>
-      </c>
-      <c r="B30">
-        <v>-1</v>
-      </c>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31">
-        <v>3001</v>
-      </c>
-      <c r="B31">
-        <v>-1</v>
-      </c>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32">
-        <v>3002</v>
-      </c>
-      <c r="B32">
-        <v>-1</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A33">
-        <v>3003</v>
-      </c>
-      <c r="B33">
-        <v>-1</v>
-      </c>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A34">
-        <v>3004</v>
-      </c>
-      <c r="B34">
-        <v>-1</v>
-      </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A35">
-        <v>3005</v>
-      </c>
-      <c r="B35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A36">
-        <v>3006</v>
-      </c>
-      <c r="B36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A37">
-        <v>3007</v>
-      </c>
-      <c r="B37">
-        <v>-1</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A38">
-        <v>3008</v>
-      </c>
-      <c r="B38">
-        <v>-1</v>
-      </c>
-      <c r="H38" s="1"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39">
-        <v>3009</v>
-      </c>
-      <c r="B39">
-        <v>-1</v>
-      </c>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40">
-        <v>3010</v>
-      </c>
-      <c r="B40">
-        <v>-1</v>
-      </c>
-      <c r="H40" s="1"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41">
-        <v>3011</v>
-      </c>
-      <c r="B41">
-        <v>-1</v>
-      </c>
-      <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42">
-        <v>3012</v>
-      </c>
-      <c r="B42">
-        <v>-1</v>
-      </c>
-      <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43">
-        <v>3013</v>
-      </c>
-      <c r="B43">
-        <v>-1</v>
-      </c>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44">
-        <v>3014</v>
-      </c>
-      <c r="B44">
-        <v>-1</v>
-      </c>
-      <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45">
-        <v>3015</v>
-      </c>
-      <c r="B45">
-        <v>-1</v>
-      </c>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46">
-        <v>3016</v>
-      </c>
-      <c r="B46">
-        <v>-1</v>
-      </c>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47">
-        <v>3017</v>
-      </c>
-      <c r="B47">
-        <v>-1</v>
-      </c>
-      <c r="H47" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/StreamingAssets/digimon.xlsx
+++ b/Assets/StreamingAssets/digimon.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProject_Github\DGM_Project\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F2282C8-4866-4E96-A53D-2BC43BE0BBAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F555D89-4EDD-49F1-9F4C-415D7AE1DF9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{8B4AE715-026E-4734-A174-D6D3038A81A1}"/>
   </bookViews>
   <sheets>
     <sheet name="PlayerStatus" sheetId="10" r:id="rId1"/>
     <sheet name="EnemyStatus" sheetId="4" r:id="rId2"/>
     <sheet name="GrowthType" sheetId="3" r:id="rId3"/>
-    <sheet name="BabyStatus" sheetId="1" r:id="rId4"/>
-    <sheet name="RookieStatus" sheetId="5" r:id="rId5"/>
-    <sheet name="ChampionStatus" sheetId="6" r:id="rId6"/>
-    <sheet name="VillageEast" sheetId="7" r:id="rId7"/>
+    <sheet name="LevelExp" sheetId="11" r:id="rId4"/>
+    <sheet name="BabyStatus" sheetId="1" r:id="rId5"/>
+    <sheet name="RookieStatus" sheetId="5" r:id="rId6"/>
+    <sheet name="ChampionStatus" sheetId="6" r:id="rId7"/>
+    <sheet name="VillageEast" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,8 +45,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1401" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1495" uniqueCount="153">
   <si>
     <t>GrowthType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -582,6 +605,38 @@
   </si>
   <si>
     <t>Togemon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tanemon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야옹몬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KorGrowthType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>균형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공격형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방어형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지능형</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>속도형</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1005,13 +1060,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9A6B5FD-6714-48F7-A243-90EB8A61A1B2}">
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="15" max="15" width="15.640625" customWidth="1"/>
+    <col min="16" max="16" width="15.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -1058,10 +1114,13 @@
         <v>0</v>
       </c>
       <c r="P1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>1001</v>
       </c>
@@ -1107,11 +1166,14 @@
       <c r="O2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q2" s="2">
         <v>2001</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>1002</v>
       </c>
@@ -1157,11 +1219,14 @@
       <c r="O3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="2">
         <v>2002</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>1003</v>
       </c>
@@ -1207,11 +1272,14 @@
       <c r="O4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q4" s="2">
         <v>2003</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>1004</v>
       </c>
@@ -1257,11 +1325,14 @@
       <c r="O5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q5" s="2">
         <v>2004</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>1005</v>
       </c>
@@ -1307,11 +1378,14 @@
       <c r="O6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q6" s="2">
         <v>2005</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <v>1006</v>
       </c>
@@ -1357,11 +1431,14 @@
       <c r="O7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q7" s="2">
         <v>2006</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2">
         <v>1007</v>
       </c>
@@ -1407,11 +1484,14 @@
       <c r="O8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q8" s="2">
         <v>2007</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>1008</v>
       </c>
@@ -1457,11 +1537,14 @@
       <c r="O9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q9" s="2">
         <v>2008</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>1009</v>
       </c>
@@ -1507,11 +1590,14 @@
       <c r="O10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q10" s="2">
         <v>2009</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>1010</v>
       </c>
@@ -1557,11 +1643,14 @@
       <c r="O11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="2">
         <v>2010</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>2001</v>
       </c>
@@ -1607,11 +1696,14 @@
       <c r="O12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q12" s="4">
         <v>3001</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>2002</v>
       </c>
@@ -1657,11 +1749,14 @@
       <c r="O13" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P13" s="4">
+      <c r="P13" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="4">
         <v>3002</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4">
         <v>2003</v>
       </c>
@@ -1707,11 +1802,14 @@
       <c r="O14" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="4">
+      <c r="P14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q14" s="4">
         <v>3003</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
         <v>2004</v>
       </c>
@@ -1757,11 +1855,14 @@
       <c r="O15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P15" s="4">
+      <c r="P15" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q15" s="4">
         <v>3004</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
         <v>2005</v>
       </c>
@@ -1807,11 +1908,14 @@
       <c r="O16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P16" s="4">
+      <c r="P16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q16" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
         <v>2006</v>
       </c>
@@ -1857,11 +1961,14 @@
       <c r="O17" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P17" s="4">
+      <c r="P17" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q17" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
         <v>2007</v>
       </c>
@@ -1907,11 +2014,14 @@
       <c r="O18" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P18" s="4">
+      <c r="P18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q18" s="4">
         <v>3007</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
         <v>2008</v>
       </c>
@@ -1957,11 +2067,14 @@
       <c r="O19" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P19" s="4">
+      <c r="P19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q19" s="4">
         <v>3008</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
         <v>2009</v>
       </c>
@@ -2007,11 +2120,14 @@
       <c r="O20" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P20" s="4">
+      <c r="P20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q20" s="4">
         <v>3009</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
         <v>2010</v>
       </c>
@@ -2057,11 +2173,14 @@
       <c r="O21" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P21" s="4">
+      <c r="P21" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q21" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
         <v>2011</v>
       </c>
@@ -2107,11 +2226,14 @@
       <c r="O22" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P22" s="4">
+      <c r="P22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q22" s="4">
         <v>3011</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
         <v>2012</v>
       </c>
@@ -2157,11 +2279,14 @@
       <c r="O23" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P23" s="4">
+      <c r="P23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" s="4">
         <v>3012</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
         <v>2013</v>
       </c>
@@ -2207,11 +2332,14 @@
       <c r="O24" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P24" s="4">
+      <c r="P24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q24" s="4">
         <v>3013</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
         <v>2014</v>
       </c>
@@ -2257,11 +2385,14 @@
       <c r="O25" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P25" s="4">
+      <c r="P25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q25" s="4">
         <v>3014</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
         <v>2015</v>
       </c>
@@ -2307,11 +2438,14 @@
       <c r="O26" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P26" s="4">
+      <c r="P26" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q26" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4">
         <v>2016</v>
       </c>
@@ -2357,11 +2491,14 @@
       <c r="O27" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P27" s="4">
+      <c r="P27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q27" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4">
         <v>2017</v>
       </c>
@@ -2407,11 +2544,14 @@
       <c r="O28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P28" s="4">
+      <c r="P28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q28" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4">
         <v>2018</v>
       </c>
@@ -2457,11 +2597,14 @@
       <c r="O29" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P29" s="4">
+      <c r="P29" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q29" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
         <v>2019</v>
       </c>
@@ -2507,11 +2650,14 @@
       <c r="O30" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P30" s="4">
+      <c r="P30" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q30" s="4">
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6">
         <v>3001</v>
       </c>
@@ -2557,11 +2703,14 @@
       <c r="O31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P31" s="6">
+      <c r="P31" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q31" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6">
         <v>3002</v>
       </c>
@@ -2607,11 +2756,14 @@
       <c r="O32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P32" s="6">
+      <c r="P32" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q32" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6">
         <v>3003</v>
       </c>
@@ -2657,11 +2809,14 @@
       <c r="O33" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P33" s="6">
+      <c r="P33" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q33" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6">
         <v>3004</v>
       </c>
@@ -2707,11 +2862,14 @@
       <c r="O34" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P34" s="6">
+      <c r="P34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q34" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6">
         <v>3007</v>
       </c>
@@ -2757,11 +2915,14 @@
       <c r="O35" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P35" s="6">
+      <c r="P35" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q35" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6">
         <v>3008</v>
       </c>
@@ -2807,11 +2968,14 @@
       <c r="O36" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P36" s="6">
+      <c r="P36" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q36" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="6">
         <v>3009</v>
       </c>
@@ -2857,11 +3021,14 @@
       <c r="O37" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P37" s="6">
+      <c r="P37" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q37" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="6">
         <v>3010</v>
       </c>
@@ -2907,11 +3074,14 @@
       <c r="O38" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P38" s="6">
+      <c r="P38" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q38" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6">
         <v>3011</v>
       </c>
@@ -2957,11 +3127,14 @@
       <c r="O39" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P39" s="6">
+      <c r="P39" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q39" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6">
         <v>3012</v>
       </c>
@@ -3007,11 +3180,14 @@
       <c r="O40" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P40" s="6">
+      <c r="P40" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q40" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="6">
         <v>3013</v>
       </c>
@@ -3057,11 +3233,14 @@
       <c r="O41" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P41" s="6">
+      <c r="P41" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q41" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="6">
         <v>3014</v>
       </c>
@@ -3107,11 +3286,14 @@
       <c r="O42" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P42" s="6">
+      <c r="P42" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q42" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="6">
         <v>3015</v>
       </c>
@@ -3157,11 +3339,14 @@
       <c r="O43" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P43" s="6">
+      <c r="P43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q43" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="6">
         <v>3016</v>
       </c>
@@ -3207,11 +3392,14 @@
       <c r="O44" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P44" s="6">
+      <c r="P44" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q44" s="6">
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="6">
         <v>3017</v>
       </c>
@@ -3257,7 +3445,10 @@
       <c r="O45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="P45" s="6">
+      <c r="P45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q45" s="6">
         <v>-1</v>
       </c>
     </row>
@@ -3269,13 +3460,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15585912-2F3A-4585-9048-DC033A32B8BC}">
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="15" max="15" width="15.5703125" customWidth="1"/>
+    <col min="16" max="16" width="15.78515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>24</v>
       </c>
@@ -3322,16 +3514,19 @@
         <v>0</v>
       </c>
       <c r="P1" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q1" t="s">
         <v>143</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>140</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>5001</v>
       </c>
@@ -3359,36 +3554,69 @@
       <c r="I2" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="2">
-        <v>150</v>
-      </c>
-      <c r="K2" s="2">
-        <v>30</v>
-      </c>
-      <c r="L2" s="2">
-        <v>30</v>
-      </c>
-      <c r="M2" s="2">
-        <v>20</v>
-      </c>
-      <c r="N2" s="2">
-        <v>20</v>
+      <c r="J2" s="2" cm="1">
+        <f t="array" ref="J2">_xlfn.SWITCH(O2,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R2-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R2-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R2-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R2-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R2-1))</f>
+        <v>255</v>
+      </c>
+      <c r="K2" s="2" cm="1">
+        <f t="array" ref="K2">_xlfn.SWITCH(O2,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R2-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R2-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R2-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R2-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R2-1))</f>
+        <v>51</v>
+      </c>
+      <c r="L2" s="2" cm="1">
+        <f t="array" ref="L2">_xlfn.SWITCH(O2,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R2-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R2-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R2-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R2-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R2-1))</f>
+        <v>51</v>
+      </c>
+      <c r="M2" s="2" cm="1">
+        <f t="array" ref="M2">_xlfn.SWITCH(O2,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R2-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R2-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R2-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R2-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R2-1))</f>
+        <v>34</v>
+      </c>
+      <c r="N2" s="2" cm="1">
+        <f t="array" ref="N2">_xlfn.SWITCH(O2,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R2-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R2-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R2-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R2-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R2-1))</f>
+        <v>34</v>
       </c>
       <c r="O2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q2" s="2">
         <v>-1</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="R2" s="2">
         <v>8</v>
       </c>
-      <c r="R2" s="2">
-        <f>1+2*(Q2-1)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S2" s="2">
+        <f>10+(R2-1)</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>5002</v>
       </c>
@@ -3416,36 +3644,69 @@
       <c r="I3" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J3" s="2">
-        <v>150</v>
-      </c>
-      <c r="K3" s="2">
-        <v>30</v>
-      </c>
-      <c r="L3" s="2">
-        <v>30</v>
-      </c>
-      <c r="M3" s="2">
-        <v>20</v>
-      </c>
-      <c r="N3" s="2">
-        <v>20</v>
+      <c r="J3" s="2" cm="1">
+        <f t="array" ref="J3">_xlfn.SWITCH(O3,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R3-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R3-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R3-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R3-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R3-1))</f>
+        <v>240</v>
+      </c>
+      <c r="K3" s="2" cm="1">
+        <f t="array" ref="K3">_xlfn.SWITCH(O3,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R3-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R3-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R3-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R3-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R3-1))</f>
+        <v>48</v>
+      </c>
+      <c r="L3" s="2" cm="1">
+        <f t="array" ref="L3">_xlfn.SWITCH(O3,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R3-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R3-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R3-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R3-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R3-1))</f>
+        <v>48</v>
+      </c>
+      <c r="M3" s="2" cm="1">
+        <f t="array" ref="M3">_xlfn.SWITCH(O3,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R3-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R3-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R3-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R3-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R3-1))</f>
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" cm="1">
+        <f t="array" ref="N3">_xlfn.SWITCH(O3,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R3-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R3-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R3-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R3-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R3-1))</f>
+        <v>32</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q3" s="2">
         <v>-1</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="R3" s="2">
         <v>7</v>
       </c>
-      <c r="R3" s="2">
-        <f t="shared" ref="R3:R12" si="0">1+2*(Q3-1)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S3" s="2">
+        <f t="shared" ref="S3:S47" si="0">10+(R3-1)</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>5003</v>
       </c>
@@ -3473,264 +3734,429 @@
       <c r="I4" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J4" s="2">
-        <v>150</v>
-      </c>
-      <c r="K4" s="2">
+      <c r="J4" s="2" cm="1">
+        <f t="array" ref="J4">_xlfn.SWITCH(O4,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R4-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R4-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R4-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R4-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R4-1))</f>
+        <v>225</v>
+      </c>
+      <c r="K4" s="2" cm="1">
+        <f t="array" ref="K4">_xlfn.SWITCH(O4,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R4-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R4-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R4-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R4-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R4-1))</f>
+        <v>45</v>
+      </c>
+      <c r="L4" s="2" cm="1">
+        <f t="array" ref="L4">_xlfn.SWITCH(O4,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R4-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R4-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R4-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R4-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R4-1))</f>
+        <v>45</v>
+      </c>
+      <c r="M4" s="2" cm="1">
+        <f t="array" ref="M4">_xlfn.SWITCH(O4,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R4-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R4-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R4-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R4-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R4-1))</f>
         <v>30</v>
       </c>
-      <c r="L4" s="2">
+      <c r="N4" s="2" cm="1">
+        <f t="array" ref="N4">_xlfn.SWITCH(O4,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R4-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R4-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R4-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R4-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R4-1))</f>
         <v>30</v>
       </c>
-      <c r="M4" s="2">
-        <v>20</v>
-      </c>
-      <c r="N4" s="2">
-        <v>20</v>
-      </c>
       <c r="O4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q4" s="2">
         <v>-1</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="R4" s="2">
         <v>6</v>
       </c>
-      <c r="R4" s="2">
+      <c r="S4" s="2">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>5004</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="2" cm="1">
+        <f t="array" ref="J5">_xlfn.SWITCH(O5,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R5-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R5-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R5-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R5-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R5-1))</f>
+        <v>270</v>
+      </c>
+      <c r="K5" s="2" cm="1">
+        <f t="array" ref="K5">_xlfn.SWITCH(O5,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R5-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R5-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R5-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R5-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R5-1))</f>
+        <v>54</v>
+      </c>
+      <c r="L5" s="2" cm="1">
+        <f t="array" ref="L5">_xlfn.SWITCH(O5,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R5-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R5-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R5-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R5-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R5-1))</f>
+        <v>54</v>
+      </c>
+      <c r="M5" s="2" cm="1">
+        <f t="array" ref="M5">_xlfn.SWITCH(O5,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R5-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R5-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R5-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R5-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R5-1))</f>
+        <v>36</v>
+      </c>
+      <c r="N5" s="2" cm="1">
+        <f t="array" ref="N5">_xlfn.SWITCH(O5,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R5-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R5-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R5-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R5-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R5-1))</f>
+        <v>36</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R5" s="2">
+        <v>9</v>
+      </c>
+      <c r="S5" s="2">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>5005</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2" cm="1">
+        <f t="array" ref="J6">_xlfn.SWITCH(O6,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R6-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R6-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R6-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R6-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R6-1))</f>
+        <v>210</v>
+      </c>
+      <c r="K6" s="2" cm="1">
+        <f t="array" ref="K6">_xlfn.SWITCH(O6,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R6-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R6-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R6-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R6-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R6-1))</f>
+        <v>42</v>
+      </c>
+      <c r="L6" s="2" cm="1">
+        <f t="array" ref="L6">_xlfn.SWITCH(O6,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R6-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R6-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R6-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R6-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R6-1))</f>
+        <v>42</v>
+      </c>
+      <c r="M6" s="2" cm="1">
+        <f t="array" ref="M6">_xlfn.SWITCH(O6,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R6-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R6-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R6-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R6-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R6-1))</f>
+        <v>28</v>
+      </c>
+      <c r="N6" s="2" cm="1">
+        <f t="array" ref="N6">_xlfn.SWITCH(O6,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R6-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R6-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R6-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R6-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R6-1))</f>
+        <v>28</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>5</v>
+      </c>
+      <c r="S6" s="2">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="2">
+        <v>5006</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" s="2" cm="1">
+        <f t="array" ref="J7">_xlfn.SWITCH(O7,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R7-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R7-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R7-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R7-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R7-1))</f>
+        <v>195</v>
+      </c>
+      <c r="K7" s="2" cm="1">
+        <f t="array" ref="K7">_xlfn.SWITCH(O7,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R7-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R7-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R7-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R7-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R7-1))</f>
+        <v>39</v>
+      </c>
+      <c r="L7" s="2" cm="1">
+        <f t="array" ref="L7">_xlfn.SWITCH(O7,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R7-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R7-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R7-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R7-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R7-1))</f>
+        <v>39</v>
+      </c>
+      <c r="M7" s="2" cm="1">
+        <f t="array" ref="M7">_xlfn.SWITCH(O7,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R7-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R7-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R7-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R7-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R7-1))</f>
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" cm="1">
+        <f t="array" ref="N7">_xlfn.SWITCH(O7,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R7-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R7-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R7-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R7-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R7-1))</f>
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="2">
+        <v>4</v>
+      </c>
+      <c r="S7" s="2">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" s="2">
+        <v>5007</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="2" cm="1">
+        <f t="array" ref="J8">_xlfn.SWITCH(O8,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R8-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R8-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R8-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R8-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R8-1))</f>
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" cm="1">
+        <f t="array" ref="K8">_xlfn.SWITCH(O8,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R8-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R8-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R8-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R8-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R8-1))</f>
+        <v>33</v>
+      </c>
+      <c r="L8" s="2" cm="1">
+        <f t="array" ref="L8">_xlfn.SWITCH(O8,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R8-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R8-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R8-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R8-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R8-1))</f>
+        <v>33</v>
+      </c>
+      <c r="M8" s="2" cm="1">
+        <f t="array" ref="M8">_xlfn.SWITCH(O8,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R8-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R8-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R8-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R8-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R8-1))</f>
+        <v>22</v>
+      </c>
+      <c r="N8" s="2" cm="1">
+        <f t="array" ref="N8">_xlfn.SWITCH(O8,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R8-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R8-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R8-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R8-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R8-1))</f>
+        <v>22</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R8" s="2">
+        <v>2</v>
+      </c>
+      <c r="S8" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="2">
-        <v>5004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" s="2">
-        <v>150</v>
-      </c>
-      <c r="K5" s="2">
-        <v>30</v>
-      </c>
-      <c r="L5" s="2">
-        <v>30</v>
-      </c>
-      <c r="M5" s="2">
-        <v>20</v>
-      </c>
-      <c r="N5" s="2">
-        <v>20</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P5" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>9</v>
-      </c>
-      <c r="R5" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="2">
-        <v>5005</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" s="2">
-        <v>150</v>
-      </c>
-      <c r="K6" s="2">
-        <v>30</v>
-      </c>
-      <c r="L6" s="2">
-        <v>30</v>
-      </c>
-      <c r="M6" s="2">
-        <v>20</v>
-      </c>
-      <c r="N6" s="2">
-        <v>20</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P6" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>5</v>
-      </c>
-      <c r="R6" s="2">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="2">
-        <v>5006</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="2">
-        <v>150</v>
-      </c>
-      <c r="K7" s="2">
-        <v>30</v>
-      </c>
-      <c r="L7" s="2">
-        <v>30</v>
-      </c>
-      <c r="M7" s="2">
-        <v>20</v>
-      </c>
-      <c r="N7" s="2">
-        <v>20</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P7" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>4</v>
-      </c>
-      <c r="R7" s="2">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="2">
-        <v>5007</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="2">
-        <v>150</v>
-      </c>
-      <c r="K8" s="2">
-        <v>30</v>
-      </c>
-      <c r="L8" s="2">
-        <v>30</v>
-      </c>
-      <c r="M8" s="2">
-        <v>20</v>
-      </c>
-      <c r="N8" s="2">
-        <v>20</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="P8" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>2</v>
-      </c>
-      <c r="R8" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2">
         <v>5008</v>
       </c>
@@ -3758,36 +4184,69 @@
       <c r="I9" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="2" cm="1">
+        <f t="array" ref="J9">_xlfn.SWITCH(O9,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R9-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R9-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R9-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R9-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R9-1))</f>
         <v>150</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="2" cm="1">
+        <f t="array" ref="K9">_xlfn.SWITCH(O9,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R9-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R9-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R9-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R9-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R9-1))</f>
         <v>30</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="2" cm="1">
+        <f t="array" ref="L9">_xlfn.SWITCH(O9,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R9-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R9-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R9-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R9-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R9-1))</f>
         <v>30</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9" s="2" cm="1">
+        <f t="array" ref="M9">_xlfn.SWITCH(O9,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R9-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R9-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R9-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R9-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R9-1))</f>
         <v>20</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="2" cm="1">
+        <f t="array" ref="N9">_xlfn.SWITCH(O9,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R9-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R9-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R9-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R9-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R9-1))</f>
         <v>20</v>
       </c>
       <c r="O9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q9" s="2">
         <v>-1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>1</v>
       </c>
-      <c r="R9" s="2">
+      <c r="S9" s="2">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2">
         <v>5009</v>
       </c>
@@ -3815,36 +4274,69 @@
       <c r="I10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J10" s="2">
-        <v>150</v>
-      </c>
-      <c r="K10" s="2">
-        <v>30</v>
-      </c>
-      <c r="L10" s="2">
-        <v>30</v>
-      </c>
-      <c r="M10" s="2">
-        <v>20</v>
-      </c>
-      <c r="N10" s="2">
-        <v>20</v>
+      <c r="J10" s="2" cm="1">
+        <f t="array" ref="J10">_xlfn.SWITCH(O10,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R10-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R10-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R10-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R10-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R10-1))</f>
+        <v>270</v>
+      </c>
+      <c r="K10" s="2" cm="1">
+        <f t="array" ref="K10">_xlfn.SWITCH(O10,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R10-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R10-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R10-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R10-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R10-1))</f>
+        <v>54</v>
+      </c>
+      <c r="L10" s="2" cm="1">
+        <f t="array" ref="L10">_xlfn.SWITCH(O10,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R10-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R10-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R10-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R10-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R10-1))</f>
+        <v>54</v>
+      </c>
+      <c r="M10" s="2" cm="1">
+        <f t="array" ref="M10">_xlfn.SWITCH(O10,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R10-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R10-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R10-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R10-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R10-1))</f>
+        <v>36</v>
+      </c>
+      <c r="N10" s="2" cm="1">
+        <f t="array" ref="N10">_xlfn.SWITCH(O10,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R10-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R10-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R10-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R10-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R10-1))</f>
+        <v>36</v>
       </c>
       <c r="O10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q10" s="2">
         <v>-1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>9</v>
       </c>
-      <c r="R10" s="2">
+      <c r="S10" s="2">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2">
         <v>5010</v>
       </c>
@@ -3872,36 +4364,69 @@
       <c r="I11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="J11" s="2">
-        <v>150</v>
-      </c>
-      <c r="K11" s="2">
-        <v>30</v>
-      </c>
-      <c r="L11" s="2">
-        <v>30</v>
-      </c>
-      <c r="M11" s="2">
-        <v>20</v>
-      </c>
-      <c r="N11" s="2">
-        <v>20</v>
+      <c r="J11" s="2" cm="1">
+        <f t="array" ref="J11">_xlfn.SWITCH(O11,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R11-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R11-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R11-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R11-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R11-1))</f>
+        <v>180</v>
+      </c>
+      <c r="K11" s="2" cm="1">
+        <f t="array" ref="K11">_xlfn.SWITCH(O11,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R11-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R11-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R11-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R11-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R11-1))</f>
+        <v>36</v>
+      </c>
+      <c r="L11" s="2" cm="1">
+        <f t="array" ref="L11">_xlfn.SWITCH(O11,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R11-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R11-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R11-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R11-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R11-1))</f>
+        <v>36</v>
+      </c>
+      <c r="M11" s="2" cm="1">
+        <f t="array" ref="M11">_xlfn.SWITCH(O11,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R11-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R11-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R11-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R11-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R11-1))</f>
+        <v>24</v>
+      </c>
+      <c r="N11" s="2" cm="1">
+        <f t="array" ref="N11">_xlfn.SWITCH(O11,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R11-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R11-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R11-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R11-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R11-1))</f>
+        <v>24</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q11" s="2">
         <v>-1</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="R11" s="2">
         <v>3</v>
       </c>
-      <c r="R11" s="2">
+      <c r="S11" s="2">
         <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="4">
         <v>6001</v>
       </c>
@@ -3929,36 +4454,69 @@
       <c r="I12" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J12" s="4">
-        <v>300</v>
-      </c>
-      <c r="K12" s="4">
-        <v>60</v>
-      </c>
-      <c r="L12" s="4">
-        <v>60</v>
-      </c>
-      <c r="M12" s="4">
-        <v>40</v>
-      </c>
-      <c r="N12" s="4">
-        <v>40</v>
+      <c r="J12" s="4" cm="1">
+        <f t="array" ref="J12">_xlfn.SWITCH(O12,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R12-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R12-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R12-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R12-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R12-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K12" s="4" cm="1">
+        <f t="array" ref="K12">_xlfn.SWITCH(O12,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R12-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R12-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R12-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R12-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R12-1))</f>
+        <v>110</v>
+      </c>
+      <c r="L12" s="4" cm="1">
+        <f t="array" ref="L12">_xlfn.SWITCH(O12,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R12-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R12-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R12-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R12-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R12-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M12" s="4" cm="1">
+        <f t="array" ref="M12">_xlfn.SWITCH(O12,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R12-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R12-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R12-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R12-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R12-1))</f>
+        <v>50</v>
+      </c>
+      <c r="N12" s="4" cm="1">
+        <f t="array" ref="N12">_xlfn.SWITCH(O12,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R12-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R12-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R12-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R12-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R12-1))</f>
+        <v>60</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P12" s="4">
+        <v>6</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q12" s="4">
         <v>-1</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="R12" s="4">
         <v>11</v>
       </c>
-      <c r="R12" s="4">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S12" s="4">
+        <f>20+(R12-1)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="4">
         <v>6002</v>
       </c>
@@ -3986,36 +4544,69 @@
       <c r="I13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J13" s="4">
-        <v>300</v>
-      </c>
-      <c r="K13" s="4">
-        <v>60</v>
-      </c>
-      <c r="L13" s="4">
-        <v>60</v>
-      </c>
-      <c r="M13" s="4">
-        <v>40</v>
-      </c>
-      <c r="N13" s="4">
-        <v>40</v>
+      <c r="J13" s="4" cm="1">
+        <f t="array" ref="J13">_xlfn.SWITCH(O13,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R13-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R13-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R13-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R13-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R13-1))</f>
+        <v>550</v>
+      </c>
+      <c r="K13" s="4" cm="1">
+        <f t="array" ref="K13">_xlfn.SWITCH(O13,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R13-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R13-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R13-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R13-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R13-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L13" s="4" cm="1">
+        <f t="array" ref="L13">_xlfn.SWITCH(O13,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R13-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R13-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R13-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R13-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R13-1))</f>
+        <v>110</v>
+      </c>
+      <c r="M13" s="4" cm="1">
+        <f t="array" ref="M13">_xlfn.SWITCH(O13,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R13-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R13-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R13-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R13-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R13-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N13" s="4" cm="1">
+        <f t="array" ref="N13">_xlfn.SWITCH(O13,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R13-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R13-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R13-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R13-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R13-1))</f>
+        <v>50</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P13" s="4">
+        <v>7</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q13" s="4">
         <v>-1</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="R13" s="4">
         <v>11</v>
       </c>
-      <c r="R13" s="4">
-        <f t="shared" ref="R13:R47" si="1">1+2*(Q13-1)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+      <c r="S13" s="4">
+        <f t="shared" ref="S13:S30" si="1">20+(R13-1)</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="4">
         <v>6003</v>
       </c>
@@ -4043,36 +4634,69 @@
       <c r="I14" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J14" s="4">
-        <v>300</v>
-      </c>
-      <c r="K14" s="4">
-        <v>60</v>
-      </c>
-      <c r="L14" s="4">
-        <v>60</v>
-      </c>
-      <c r="M14" s="4">
-        <v>40</v>
-      </c>
-      <c r="N14" s="4">
-        <v>40</v>
+      <c r="J14" s="4" cm="1">
+        <f t="array" ref="J14">_xlfn.SWITCH(O14,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R14-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R14-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R14-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R14-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R14-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K14" s="4" cm="1">
+        <f t="array" ref="K14">_xlfn.SWITCH(O14,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R14-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R14-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R14-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R14-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R14-1))</f>
+        <v>70</v>
+      </c>
+      <c r="L14" s="4" cm="1">
+        <f t="array" ref="L14">_xlfn.SWITCH(O14,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R14-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R14-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R14-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R14-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R14-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M14" s="4" cm="1">
+        <f t="array" ref="M14">_xlfn.SWITCH(O14,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R14-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R14-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R14-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R14-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R14-1))</f>
+        <v>90</v>
+      </c>
+      <c r="N14" s="4" cm="1">
+        <f t="array" ref="N14">_xlfn.SWITCH(O14,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R14-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R14-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R14-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R14-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R14-1))</f>
+        <v>60</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P14" s="4">
+        <v>8</v>
+      </c>
+      <c r="P14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q14" s="4">
         <v>-1</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="4">
         <v>11</v>
       </c>
-      <c r="R14" s="4">
+      <c r="S14" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="4">
         <v>6004</v>
       </c>
@@ -4100,36 +4724,69 @@
       <c r="I15" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J15" s="4">
-        <v>300</v>
-      </c>
-      <c r="K15" s="4">
-        <v>60</v>
-      </c>
-      <c r="L15" s="4">
-        <v>60</v>
-      </c>
-      <c r="M15" s="4">
-        <v>40</v>
-      </c>
-      <c r="N15" s="4">
-        <v>40</v>
+      <c r="J15" s="4" cm="1">
+        <f t="array" ref="J15">_xlfn.SWITCH(O15,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R15-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R15-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R15-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R15-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R15-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K15" s="4" cm="1">
+        <f t="array" ref="K15">_xlfn.SWITCH(O15,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R15-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R15-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R15-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R15-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R15-1))</f>
+        <v>70</v>
+      </c>
+      <c r="L15" s="4" cm="1">
+        <f t="array" ref="L15">_xlfn.SWITCH(O15,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R15-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R15-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R15-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R15-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R15-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M15" s="4" cm="1">
+        <f t="array" ref="M15">_xlfn.SWITCH(O15,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R15-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R15-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R15-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R15-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R15-1))</f>
+        <v>90</v>
+      </c>
+      <c r="N15" s="4" cm="1">
+        <f t="array" ref="N15">_xlfn.SWITCH(O15,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R15-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R15-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R15-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R15-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R15-1))</f>
+        <v>60</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P15" s="4">
+        <v>8</v>
+      </c>
+      <c r="P15" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q15" s="4">
         <v>-1</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="4">
         <v>11</v>
       </c>
-      <c r="R15" s="4">
+      <c r="S15" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="4">
         <v>6005</v>
       </c>
@@ -4157,36 +4814,69 @@
       <c r="I16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J16" s="4">
-        <v>300</v>
-      </c>
-      <c r="K16" s="4">
-        <v>60</v>
-      </c>
-      <c r="L16" s="4">
-        <v>60</v>
-      </c>
-      <c r="M16" s="4">
-        <v>40</v>
-      </c>
-      <c r="N16" s="4">
-        <v>40</v>
+      <c r="J16" s="4" cm="1">
+        <f t="array" ref="J16">_xlfn.SWITCH(O16,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R16-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R16-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R16-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R16-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R16-1))</f>
+        <v>350</v>
+      </c>
+      <c r="K16" s="4" cm="1">
+        <f t="array" ref="K16">_xlfn.SWITCH(O16,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R16-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R16-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R16-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R16-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R16-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L16" s="4" cm="1">
+        <f t="array" ref="L16">_xlfn.SWITCH(O16,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R16-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R16-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R16-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R16-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R16-1))</f>
+        <v>70</v>
+      </c>
+      <c r="M16" s="4" cm="1">
+        <f t="array" ref="M16">_xlfn.SWITCH(O16,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R16-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R16-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R16-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R16-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R16-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N16" s="4" cm="1">
+        <f t="array" ref="N16">_xlfn.SWITCH(O16,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R16-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R16-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R16-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R16-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R16-1))</f>
+        <v>90</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P16" s="4">
+        <v>9</v>
+      </c>
+      <c r="P16" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q16" s="4">
         <v>-1</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="4">
         <v>11</v>
       </c>
-      <c r="R16" s="4">
+      <c r="S16" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="4">
         <v>6006</v>
       </c>
@@ -4214,36 +4904,69 @@
       <c r="I17" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J17" s="4">
-        <v>300</v>
-      </c>
-      <c r="K17" s="4">
-        <v>60</v>
-      </c>
-      <c r="L17" s="4">
-        <v>60</v>
-      </c>
-      <c r="M17" s="4">
-        <v>40</v>
-      </c>
-      <c r="N17" s="4">
-        <v>40</v>
+      <c r="J17" s="4" cm="1">
+        <f t="array" ref="J17">_xlfn.SWITCH(O17,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R17-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R17-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R17-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R17-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R17-1))</f>
+        <v>350</v>
+      </c>
+      <c r="K17" s="4" cm="1">
+        <f t="array" ref="K17">_xlfn.SWITCH(O17,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R17-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R17-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R17-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R17-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R17-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L17" s="4" cm="1">
+        <f t="array" ref="L17">_xlfn.SWITCH(O17,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R17-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R17-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R17-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R17-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R17-1))</f>
+        <v>70</v>
+      </c>
+      <c r="M17" s="4" cm="1">
+        <f t="array" ref="M17">_xlfn.SWITCH(O17,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R17-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R17-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R17-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R17-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R17-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N17" s="4" cm="1">
+        <f t="array" ref="N17">_xlfn.SWITCH(O17,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R17-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R17-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R17-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R17-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R17-1))</f>
+        <v>90</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P17" s="4">
+        <v>9</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q17" s="4">
         <v>-1</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="4">
         <v>11</v>
       </c>
-      <c r="R17" s="4">
+      <c r="S17" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="4">
         <v>6007</v>
       </c>
@@ -4271,36 +4994,69 @@
       <c r="I18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J18" s="4">
-        <v>300</v>
-      </c>
-      <c r="K18" s="4">
-        <v>60</v>
-      </c>
-      <c r="L18" s="4">
-        <v>60</v>
-      </c>
-      <c r="M18" s="4">
-        <v>40</v>
-      </c>
-      <c r="N18" s="4">
-        <v>40</v>
+      <c r="J18" s="4" cm="1">
+        <f t="array" ref="J18">_xlfn.SWITCH(O18,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R18-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R18-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R18-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R18-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R18-1))</f>
+        <v>550</v>
+      </c>
+      <c r="K18" s="4" cm="1">
+        <f t="array" ref="K18">_xlfn.SWITCH(O18,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R18-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R18-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R18-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R18-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R18-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L18" s="4" cm="1">
+        <f t="array" ref="L18">_xlfn.SWITCH(O18,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R18-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R18-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R18-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R18-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R18-1))</f>
+        <v>110</v>
+      </c>
+      <c r="M18" s="4" cm="1">
+        <f t="array" ref="M18">_xlfn.SWITCH(O18,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R18-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R18-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R18-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R18-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R18-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N18" s="4" cm="1">
+        <f t="array" ref="N18">_xlfn.SWITCH(O18,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R18-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R18-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R18-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R18-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R18-1))</f>
+        <v>50</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P18" s="4">
+        <v>7</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q18" s="4">
         <v>-1</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="4">
         <v>11</v>
       </c>
-      <c r="R18" s="4">
+      <c r="S18" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="4">
         <v>6008</v>
       </c>
@@ -4328,36 +5084,69 @@
       <c r="I19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J19" s="4">
-        <v>300</v>
-      </c>
-      <c r="K19" s="4">
-        <v>60</v>
-      </c>
-      <c r="L19" s="4">
-        <v>60</v>
-      </c>
-      <c r="M19" s="4">
-        <v>40</v>
-      </c>
-      <c r="N19" s="4">
-        <v>40</v>
+      <c r="J19" s="4" cm="1">
+        <f t="array" ref="J19">_xlfn.SWITCH(O19,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R19-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R19-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R19-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R19-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R19-1))</f>
+        <v>550</v>
+      </c>
+      <c r="K19" s="4" cm="1">
+        <f t="array" ref="K19">_xlfn.SWITCH(O19,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R19-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R19-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R19-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R19-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R19-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L19" s="4" cm="1">
+        <f t="array" ref="L19">_xlfn.SWITCH(O19,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R19-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R19-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R19-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R19-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R19-1))</f>
+        <v>110</v>
+      </c>
+      <c r="M19" s="4" cm="1">
+        <f t="array" ref="M19">_xlfn.SWITCH(O19,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R19-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R19-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R19-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R19-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R19-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N19" s="4" cm="1">
+        <f t="array" ref="N19">_xlfn.SWITCH(O19,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R19-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R19-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R19-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R19-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R19-1))</f>
+        <v>50</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P19" s="4">
+        <v>7</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q19" s="4">
         <v>-1</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="4">
         <v>11</v>
       </c>
-      <c r="R19" s="4">
+      <c r="S19" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="4">
         <v>6009</v>
       </c>
@@ -4385,36 +5174,69 @@
       <c r="I20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J20" s="4">
-        <v>300</v>
-      </c>
-      <c r="K20" s="4">
-        <v>60</v>
-      </c>
-      <c r="L20" s="4">
-        <v>60</v>
-      </c>
-      <c r="M20" s="4">
-        <v>40</v>
-      </c>
-      <c r="N20" s="4">
-        <v>40</v>
+      <c r="J20" s="4" cm="1">
+        <f t="array" ref="J20">_xlfn.SWITCH(O20,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R20-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R20-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R20-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R20-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R20-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K20" s="4" cm="1">
+        <f t="array" ref="K20">_xlfn.SWITCH(O20,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R20-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R20-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R20-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R20-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R20-1))</f>
+        <v>70</v>
+      </c>
+      <c r="L20" s="4" cm="1">
+        <f t="array" ref="L20">_xlfn.SWITCH(O20,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R20-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R20-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R20-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R20-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R20-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M20" s="4" cm="1">
+        <f t="array" ref="M20">_xlfn.SWITCH(O20,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R20-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R20-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R20-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R20-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R20-1))</f>
+        <v>90</v>
+      </c>
+      <c r="N20" s="4" cm="1">
+        <f t="array" ref="N20">_xlfn.SWITCH(O20,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R20-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R20-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R20-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R20-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R20-1))</f>
+        <v>60</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P20" s="4">
+        <v>8</v>
+      </c>
+      <c r="P20" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q20" s="4">
         <v>-1</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="4">
         <v>11</v>
       </c>
-      <c r="R20" s="4">
+      <c r="S20" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="4">
         <v>6010</v>
       </c>
@@ -4442,36 +5264,69 @@
       <c r="I21" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J21" s="4">
-        <v>300</v>
-      </c>
-      <c r="K21" s="4">
-        <v>60</v>
-      </c>
-      <c r="L21" s="4">
-        <v>60</v>
-      </c>
-      <c r="M21" s="4">
-        <v>40</v>
-      </c>
-      <c r="N21" s="4">
-        <v>40</v>
+      <c r="J21" s="4" cm="1">
+        <f t="array" ref="J21">_xlfn.SWITCH(O21,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R21-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R21-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R21-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R21-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R21-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K21" s="4" cm="1">
+        <f t="array" ref="K21">_xlfn.SWITCH(O21,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R21-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R21-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R21-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R21-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R21-1))</f>
+        <v>110</v>
+      </c>
+      <c r="L21" s="4" cm="1">
+        <f t="array" ref="L21">_xlfn.SWITCH(O21,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R21-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R21-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R21-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R21-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R21-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M21" s="4" cm="1">
+        <f t="array" ref="M21">_xlfn.SWITCH(O21,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R21-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R21-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R21-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R21-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R21-1))</f>
+        <v>50</v>
+      </c>
+      <c r="N21" s="4" cm="1">
+        <f t="array" ref="N21">_xlfn.SWITCH(O21,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R21-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R21-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R21-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R21-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R21-1))</f>
+        <v>60</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P21" s="4">
+        <v>6</v>
+      </c>
+      <c r="P21" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q21" s="4">
         <v>-1</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="4">
         <v>11</v>
       </c>
-      <c r="R21" s="4">
+      <c r="S21" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="4">
         <v>6011</v>
       </c>
@@ -4499,36 +5354,69 @@
       <c r="I22" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J22" s="4">
-        <v>300</v>
-      </c>
-      <c r="K22" s="4">
-        <v>60</v>
-      </c>
-      <c r="L22" s="4">
-        <v>60</v>
-      </c>
-      <c r="M22" s="4">
-        <v>40</v>
-      </c>
-      <c r="N22" s="4">
-        <v>40</v>
+      <c r="J22" s="4" cm="1">
+        <f t="array" ref="J22">_xlfn.SWITCH(O22,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R22-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R22-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R22-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R22-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R22-1))</f>
+        <v>350</v>
+      </c>
+      <c r="K22" s="4" cm="1">
+        <f t="array" ref="K22">_xlfn.SWITCH(O22,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R22-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R22-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R22-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R22-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R22-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L22" s="4" cm="1">
+        <f t="array" ref="L22">_xlfn.SWITCH(O22,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R22-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R22-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R22-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R22-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R22-1))</f>
+        <v>70</v>
+      </c>
+      <c r="M22" s="4" cm="1">
+        <f t="array" ref="M22">_xlfn.SWITCH(O22,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R22-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R22-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R22-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R22-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R22-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N22" s="4" cm="1">
+        <f t="array" ref="N22">_xlfn.SWITCH(O22,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R22-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R22-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R22-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R22-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R22-1))</f>
+        <v>90</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P22" s="4">
+        <v>9</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q22" s="4">
         <v>-1</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="R22" s="4">
         <v>11</v>
       </c>
-      <c r="R22" s="4">
+      <c r="S22" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="4">
         <v>6012</v>
       </c>
@@ -4556,36 +5444,69 @@
       <c r="I23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J23" s="4">
-        <v>300</v>
-      </c>
-      <c r="K23" s="4">
-        <v>60</v>
-      </c>
-      <c r="L23" s="4">
-        <v>60</v>
-      </c>
-      <c r="M23" s="4">
-        <v>40</v>
-      </c>
-      <c r="N23" s="4">
-        <v>40</v>
+      <c r="J23" s="4" cm="1">
+        <f t="array" ref="J23">_xlfn.SWITCH(O23,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R23-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R23-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R23-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R23-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R23-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K23" s="4" cm="1">
+        <f t="array" ref="K23">_xlfn.SWITCH(O23,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R23-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R23-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R23-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R23-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R23-1))</f>
+        <v>110</v>
+      </c>
+      <c r="L23" s="4" cm="1">
+        <f t="array" ref="L23">_xlfn.SWITCH(O23,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R23-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R23-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R23-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R23-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R23-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M23" s="4" cm="1">
+        <f t="array" ref="M23">_xlfn.SWITCH(O23,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R23-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R23-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R23-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R23-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R23-1))</f>
+        <v>50</v>
+      </c>
+      <c r="N23" s="4" cm="1">
+        <f t="array" ref="N23">_xlfn.SWITCH(O23,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R23-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R23-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R23-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R23-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R23-1))</f>
+        <v>60</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P23" s="4">
+        <v>6</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q23" s="4">
         <v>-1</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="R23" s="4">
         <v>11</v>
       </c>
-      <c r="R23" s="4">
+      <c r="S23" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="4">
         <v>6013</v>
       </c>
@@ -4613,36 +5534,69 @@
       <c r="I24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J24" s="4">
-        <v>300</v>
-      </c>
-      <c r="K24" s="4">
-        <v>60</v>
-      </c>
-      <c r="L24" s="4">
-        <v>60</v>
-      </c>
-      <c r="M24" s="4">
-        <v>40</v>
-      </c>
-      <c r="N24" s="4">
-        <v>40</v>
+      <c r="J24" s="4" cm="1">
+        <f t="array" ref="J24">_xlfn.SWITCH(O24,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R24-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R24-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R24-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R24-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R24-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K24" s="4" cm="1">
+        <f t="array" ref="K24">_xlfn.SWITCH(O24,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R24-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R24-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R24-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R24-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R24-1))</f>
+        <v>110</v>
+      </c>
+      <c r="L24" s="4" cm="1">
+        <f t="array" ref="L24">_xlfn.SWITCH(O24,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R24-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R24-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R24-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R24-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R24-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M24" s="4" cm="1">
+        <f t="array" ref="M24">_xlfn.SWITCH(O24,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R24-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R24-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R24-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R24-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R24-1))</f>
+        <v>50</v>
+      </c>
+      <c r="N24" s="4" cm="1">
+        <f t="array" ref="N24">_xlfn.SWITCH(O24,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R24-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R24-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R24-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R24-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R24-1))</f>
+        <v>60</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P24" s="4">
+        <v>6</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q24" s="4">
         <v>-1</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="R24" s="4">
         <v>11</v>
       </c>
-      <c r="R24" s="4">
+      <c r="S24" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="4">
         <v>6014</v>
       </c>
@@ -4670,36 +5624,69 @@
       <c r="I25" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="J25" s="4">
-        <v>300</v>
-      </c>
-      <c r="K25" s="4">
-        <v>60</v>
-      </c>
-      <c r="L25" s="4">
-        <v>60</v>
-      </c>
-      <c r="M25" s="4">
-        <v>40</v>
-      </c>
-      <c r="N25" s="4">
-        <v>40</v>
+      <c r="J25" s="4" cm="1">
+        <f t="array" ref="J25">_xlfn.SWITCH(O25,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R25-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R25-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R25-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R25-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R25-1))</f>
+        <v>350</v>
+      </c>
+      <c r="K25" s="4" cm="1">
+        <f t="array" ref="K25">_xlfn.SWITCH(O25,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R25-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R25-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R25-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R25-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R25-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L25" s="4" cm="1">
+        <f t="array" ref="L25">_xlfn.SWITCH(O25,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R25-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R25-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R25-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R25-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R25-1))</f>
+        <v>70</v>
+      </c>
+      <c r="M25" s="4" cm="1">
+        <f t="array" ref="M25">_xlfn.SWITCH(O25,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R25-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R25-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R25-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R25-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R25-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N25" s="4" cm="1">
+        <f t="array" ref="N25">_xlfn.SWITCH(O25,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R25-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R25-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R25-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R25-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R25-1))</f>
+        <v>90</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P25" s="4">
+        <v>9</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q25" s="4">
         <v>-1</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="R25" s="4">
         <v>11</v>
       </c>
-      <c r="R25" s="4">
+      <c r="S25" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="4">
         <v>6015</v>
       </c>
@@ -4727,36 +5714,69 @@
       <c r="I26" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J26" s="4">
-        <v>300</v>
-      </c>
-      <c r="K26" s="4">
-        <v>60</v>
-      </c>
-      <c r="L26" s="4">
-        <v>60</v>
-      </c>
-      <c r="M26" s="4">
-        <v>40</v>
-      </c>
-      <c r="N26" s="4">
-        <v>40</v>
+      <c r="J26" s="4" cm="1">
+        <f t="array" ref="J26">_xlfn.SWITCH(O26,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R26-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R26-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R26-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R26-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R26-1))</f>
+        <v>550</v>
+      </c>
+      <c r="K26" s="4" cm="1">
+        <f t="array" ref="K26">_xlfn.SWITCH(O26,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R26-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R26-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R26-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R26-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R26-1))</f>
+        <v>80</v>
+      </c>
+      <c r="L26" s="4" cm="1">
+        <f t="array" ref="L26">_xlfn.SWITCH(O26,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R26-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R26-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R26-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R26-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R26-1))</f>
+        <v>110</v>
+      </c>
+      <c r="M26" s="4" cm="1">
+        <f t="array" ref="M26">_xlfn.SWITCH(O26,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R26-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R26-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R26-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R26-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R26-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N26" s="4" cm="1">
+        <f t="array" ref="N26">_xlfn.SWITCH(O26,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R26-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R26-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R26-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R26-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R26-1))</f>
+        <v>50</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P26" s="4">
+        <v>7</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q26" s="4">
         <v>-1</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="R26" s="4">
         <v>11</v>
       </c>
-      <c r="R26" s="4">
+      <c r="S26" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="4">
         <v>6016</v>
       </c>
@@ -4784,36 +5804,69 @@
       <c r="I27" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J27" s="4">
-        <v>300</v>
-      </c>
-      <c r="K27" s="4">
-        <v>60</v>
-      </c>
-      <c r="L27" s="4">
-        <v>60</v>
-      </c>
-      <c r="M27" s="4">
-        <v>40</v>
-      </c>
-      <c r="N27" s="4">
-        <v>40</v>
+      <c r="J27" s="4" cm="1">
+        <f t="array" ref="J27">_xlfn.SWITCH(O27,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R27-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R27-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R27-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R27-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R27-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K27" s="4" cm="1">
+        <f t="array" ref="K27">_xlfn.SWITCH(O27,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R27-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R27-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R27-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R27-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R27-1))</f>
+        <v>70</v>
+      </c>
+      <c r="L27" s="4" cm="1">
+        <f t="array" ref="L27">_xlfn.SWITCH(O27,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R27-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R27-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R27-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R27-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R27-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M27" s="4" cm="1">
+        <f t="array" ref="M27">_xlfn.SWITCH(O27,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R27-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R27-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R27-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R27-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R27-1))</f>
+        <v>90</v>
+      </c>
+      <c r="N27" s="4" cm="1">
+        <f t="array" ref="N27">_xlfn.SWITCH(O27,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R27-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R27-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R27-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R27-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R27-1))</f>
+        <v>60</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P27" s="4">
+        <v>8</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q27" s="4">
         <v>-1</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="R27" s="4">
         <v>11</v>
       </c>
-      <c r="R27" s="4">
+      <c r="S27" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="4">
         <v>6017</v>
       </c>
@@ -4841,36 +5894,69 @@
       <c r="I28" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J28" s="4">
-        <v>300</v>
-      </c>
-      <c r="K28" s="4">
-        <v>60</v>
-      </c>
-      <c r="L28" s="4">
-        <v>60</v>
-      </c>
-      <c r="M28" s="4">
-        <v>40</v>
-      </c>
-      <c r="N28" s="4">
-        <v>40</v>
+      <c r="J28" s="4" cm="1">
+        <f t="array" ref="J28">_xlfn.SWITCH(O28,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R28-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R28-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R28-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R28-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R28-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K28" s="4" cm="1">
+        <f t="array" ref="K28">_xlfn.SWITCH(O28,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R28-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R28-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R28-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R28-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R28-1))</f>
+        <v>110</v>
+      </c>
+      <c r="L28" s="4" cm="1">
+        <f t="array" ref="L28">_xlfn.SWITCH(O28,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R28-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R28-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R28-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R28-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R28-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M28" s="4" cm="1">
+        <f t="array" ref="M28">_xlfn.SWITCH(O28,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R28-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R28-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R28-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R28-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R28-1))</f>
+        <v>50</v>
+      </c>
+      <c r="N28" s="4" cm="1">
+        <f t="array" ref="N28">_xlfn.SWITCH(O28,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R28-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R28-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R28-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R28-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R28-1))</f>
+        <v>60</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P28" s="4">
+        <v>6</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q28" s="4">
         <v>-1</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="R28" s="4">
         <v>11</v>
       </c>
-      <c r="R28" s="4">
+      <c r="S28" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="4">
         <v>6018</v>
       </c>
@@ -4898,36 +5984,69 @@
       <c r="I29" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J29" s="4">
-        <v>300</v>
-      </c>
-      <c r="K29" s="4">
-        <v>60</v>
-      </c>
-      <c r="L29" s="4">
-        <v>60</v>
-      </c>
-      <c r="M29" s="4">
-        <v>40</v>
-      </c>
-      <c r="N29" s="4">
-        <v>40</v>
+      <c r="J29" s="4" cm="1">
+        <f t="array" ref="J29">_xlfn.SWITCH(O29,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R29-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R29-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R29-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R29-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R29-1))</f>
+        <v>400</v>
+      </c>
+      <c r="K29" s="4" cm="1">
+        <f t="array" ref="K29">_xlfn.SWITCH(O29,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R29-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R29-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R29-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R29-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R29-1))</f>
+        <v>70</v>
+      </c>
+      <c r="L29" s="4" cm="1">
+        <f t="array" ref="L29">_xlfn.SWITCH(O29,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R29-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R29-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R29-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R29-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R29-1))</f>
+        <v>80</v>
+      </c>
+      <c r="M29" s="4" cm="1">
+        <f t="array" ref="M29">_xlfn.SWITCH(O29,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R29-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R29-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R29-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R29-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R29-1))</f>
+        <v>90</v>
+      </c>
+      <c r="N29" s="4" cm="1">
+        <f t="array" ref="N29">_xlfn.SWITCH(O29,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R29-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R29-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R29-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R29-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R29-1))</f>
+        <v>60</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P29" s="4">
+        <v>8</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q29" s="4">
         <v>-1</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="R29" s="4">
         <v>11</v>
       </c>
-      <c r="R29" s="4">
+      <c r="S29" s="4">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="4">
         <v>6019</v>
       </c>
@@ -4955,36 +6074,69 @@
       <c r="I30" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="J30" s="4">
-        <v>300</v>
-      </c>
-      <c r="K30" s="4">
-        <v>60</v>
-      </c>
-      <c r="L30" s="4">
-        <v>60</v>
-      </c>
-      <c r="M30" s="4">
-        <v>40</v>
-      </c>
-      <c r="N30" s="4">
-        <v>40</v>
+      <c r="J30" s="4" cm="1">
+        <f t="array" ref="J30">_xlfn.SWITCH(O30,
+"Balance",300+GrowthType!$B$2*(EnemyStatus!R30-1),
+"Atype",300+GrowthType!$B$3*(EnemyStatus!R30-1),
+"Dtype",300+GrowthType!$B$4*(EnemyStatus!R30-1),
+"Itype",300+GrowthType!$B$5*(EnemyStatus!R30-1),
+"Stype",300+GrowthType!$B$6*(EnemyStatus!R30-1))</f>
+        <v>480</v>
+      </c>
+      <c r="K30" s="4" cm="1">
+        <f t="array" ref="K30">_xlfn.SWITCH(O30,
+ "Balance", 60+GrowthType!$C$2*(EnemyStatus!R30-1),
+ "Atype",   60+GrowthType!$C$3*(EnemyStatus!R30-1),
+ "Dtype",   60+GrowthType!$C$4*(EnemyStatus!R30-1),
+ "Itype",   60+GrowthType!$C$5*(EnemyStatus!R30-1),
+ "Stype",   60+GrowthType!$C$6*(EnemyStatus!R30-1))</f>
+        <v>78</v>
+      </c>
+      <c r="L30" s="4" cm="1">
+        <f t="array" ref="L30">_xlfn.SWITCH(O30,
+ "Balance", 60+GrowthType!$D$2*(EnemyStatus!R30-1),
+ "Atype",   60+GrowthType!$D$3*(EnemyStatus!R30-1),
+ "Dtype",   60+GrowthType!$D$4*(EnemyStatus!R30-1),
+ "Itype",   60+GrowthType!$D$5*(EnemyStatus!R30-1),
+ "Stype",   60+GrowthType!$D$6*(EnemyStatus!R30-1))</f>
+        <v>96</v>
+      </c>
+      <c r="M30" s="4" cm="1">
+        <f t="array" ref="M30">_xlfn.SWITCH(O30,
+ "Balance", 40+GrowthType!$E$2*(EnemyStatus!R30-1),
+ "Atype",   40+GrowthType!$E$3*(EnemyStatus!R30-1),
+ "Dtype",   40+GrowthType!$E$4*(EnemyStatus!R30-1),
+ "Itype",   40+GrowthType!$E$5*(EnemyStatus!R30-1),
+ "Stype",   40+GrowthType!$E$6*(EnemyStatus!R30-1))</f>
+        <v>130</v>
+      </c>
+      <c r="N30" s="4" cm="1">
+        <f t="array" ref="N30">_xlfn.SWITCH(O30,
+ "Balance", 40+GrowthType!$F$2*(EnemyStatus!R30-1),
+ "Atype",   40+GrowthType!$F$3*(EnemyStatus!R30-1),
+ "Dtype",   40+GrowthType!$F$4*(EnemyStatus!R30-1),
+ "Itype",   40+GrowthType!$F$5*(EnemyStatus!R30-1),
+ "Stype",   40+GrowthType!$F$6*(EnemyStatus!R30-1))</f>
+        <v>76</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="P30" s="4">
+        <v>8</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="Q30" s="4">
         <v>-1</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="R30" s="4">
         <v>19</v>
       </c>
-      <c r="R30" s="4">
+      <c r="S30" s="4">
         <f t="shared" si="1"/>
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6">
         <v>7001</v>
       </c>
@@ -5012,36 +6164,69 @@
       <c r="I31" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J31" s="6">
-        <v>500</v>
-      </c>
-      <c r="K31" s="6">
-        <v>100</v>
-      </c>
-      <c r="L31" s="6">
-        <v>100</v>
-      </c>
-      <c r="M31" s="6">
+      <c r="J31" s="6" cm="1">
+        <f t="array" ref="J31">_xlfn.SWITCH(O31,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R31-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R31-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R31-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R31-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R31-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K31" s="6" cm="1">
+        <f t="array" ref="K31">_xlfn.SWITCH(O31,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R31-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R31-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R31-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R31-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R31-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L31" s="6" cm="1">
+        <f t="array" ref="L31">_xlfn.SWITCH(O31,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R31-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R31-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R31-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R31-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R31-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M31" s="6" cm="1">
+        <f t="array" ref="M31">_xlfn.SWITCH(O31,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R31-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R31-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R31-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R31-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R31-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N31" s="6" cm="1">
+        <f t="array" ref="N31">_xlfn.SWITCH(O31,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R31-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R31-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R31-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R31-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R31-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q31" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R31" s="6">
+        <v>21</v>
+      </c>
+      <c r="S31" s="6">
+        <f>50+(R31-1)</f>
         <v>70</v>
       </c>
-      <c r="N31" s="6">
-        <v>70</v>
-      </c>
-      <c r="O31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P31" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>21</v>
-      </c>
-      <c r="R31" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="6">
         <v>7002</v>
       </c>
@@ -5069,36 +6254,69 @@
       <c r="I32" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J32" s="6">
-        <v>500</v>
-      </c>
-      <c r="K32" s="6">
-        <v>100</v>
-      </c>
-      <c r="L32" s="6">
-        <v>100</v>
-      </c>
-      <c r="M32" s="6">
+      <c r="J32" s="6" cm="1">
+        <f t="array" ref="J32">_xlfn.SWITCH(O32,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R32-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R32-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R32-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R32-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R32-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K32" s="6" cm="1">
+        <f t="array" ref="K32">_xlfn.SWITCH(O32,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R32-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R32-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R32-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R32-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R32-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L32" s="6" cm="1">
+        <f t="array" ref="L32">_xlfn.SWITCH(O32,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R32-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R32-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R32-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R32-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R32-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M32" s="6" cm="1">
+        <f t="array" ref="M32">_xlfn.SWITCH(O32,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R32-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R32-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R32-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R32-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R32-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N32" s="6" cm="1">
+        <f t="array" ref="N32">_xlfn.SWITCH(O32,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R32-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R32-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R32-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R32-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R32-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R32" s="6">
+        <v>21</v>
+      </c>
+      <c r="S32" s="6">
+        <f t="shared" ref="S32:S47" si="2">50+(R32-1)</f>
         <v>70</v>
       </c>
-      <c r="N32" s="6">
-        <v>70</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P32" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q32" s="6">
-        <v>21</v>
-      </c>
-      <c r="R32" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6">
         <v>7003</v>
       </c>
@@ -5126,36 +6344,69 @@
       <c r="I33" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="6">
-        <v>500</v>
-      </c>
-      <c r="K33" s="6">
-        <v>100</v>
-      </c>
-      <c r="L33" s="6">
-        <v>100</v>
-      </c>
-      <c r="M33" s="6">
+      <c r="J33" s="6" cm="1">
+        <f t="array" ref="J33">_xlfn.SWITCH(O33,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R33-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R33-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R33-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R33-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R33-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K33" s="6" cm="1">
+        <f t="array" ref="K33">_xlfn.SWITCH(O33,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R33-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R33-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R33-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R33-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R33-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L33" s="6" cm="1">
+        <f t="array" ref="L33">_xlfn.SWITCH(O33,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R33-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R33-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R33-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R33-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R33-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M33" s="6" cm="1">
+        <f t="array" ref="M33">_xlfn.SWITCH(O33,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R33-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R33-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R33-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R33-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R33-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N33" s="6" cm="1">
+        <f t="array" ref="N33">_xlfn.SWITCH(O33,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R33-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R33-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R33-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R33-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R33-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R33" s="6">
+        <v>21</v>
+      </c>
+      <c r="S33" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N33" s="6">
-        <v>70</v>
-      </c>
-      <c r="O33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P33" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q33" s="6">
-        <v>21</v>
-      </c>
-      <c r="R33" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="6">
         <v>7004</v>
       </c>
@@ -5183,36 +6434,69 @@
       <c r="I34" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="6">
-        <v>500</v>
-      </c>
-      <c r="K34" s="6">
-        <v>100</v>
-      </c>
-      <c r="L34" s="6">
-        <v>100</v>
-      </c>
-      <c r="M34" s="6">
+      <c r="J34" s="6" cm="1">
+        <f t="array" ref="J34">_xlfn.SWITCH(O34,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R34-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R34-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R34-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R34-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R34-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K34" s="6" cm="1">
+        <f t="array" ref="K34">_xlfn.SWITCH(O34,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R34-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R34-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R34-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R34-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R34-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L34" s="6" cm="1">
+        <f t="array" ref="L34">_xlfn.SWITCH(O34,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R34-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R34-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R34-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R34-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R34-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M34" s="6" cm="1">
+        <f t="array" ref="M34">_xlfn.SWITCH(O34,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R34-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R34-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R34-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R34-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R34-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N34" s="6" cm="1">
+        <f t="array" ref="N34">_xlfn.SWITCH(O34,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R34-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R34-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R34-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R34-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R34-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R34" s="6">
+        <v>21</v>
+      </c>
+      <c r="S34" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N34" s="6">
-        <v>70</v>
-      </c>
-      <c r="O34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P34" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>21</v>
-      </c>
-      <c r="R34" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="6">
         <v>7005</v>
       </c>
@@ -5240,36 +6524,69 @@
       <c r="I35" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J35" s="6">
-        <v>500</v>
-      </c>
-      <c r="K35" s="6">
-        <v>100</v>
-      </c>
-      <c r="L35" s="6">
-        <v>100</v>
-      </c>
-      <c r="M35" s="6">
+      <c r="J35" s="6" cm="1">
+        <f t="array" ref="J35">_xlfn.SWITCH(O35,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R35-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R35-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R35-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R35-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R35-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K35" s="6" cm="1">
+        <f t="array" ref="K35">_xlfn.SWITCH(O35,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R35-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R35-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R35-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R35-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R35-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L35" s="6" cm="1">
+        <f t="array" ref="L35">_xlfn.SWITCH(O35,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R35-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R35-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R35-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R35-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R35-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M35" s="6" cm="1">
+        <f t="array" ref="M35">_xlfn.SWITCH(O35,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R35-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R35-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R35-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R35-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R35-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N35" s="6" cm="1">
+        <f t="array" ref="N35">_xlfn.SWITCH(O35,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R35-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R35-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R35-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R35-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R35-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q35" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R35" s="6">
+        <v>21</v>
+      </c>
+      <c r="S35" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N35" s="6">
-        <v>70</v>
-      </c>
-      <c r="O35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P35" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q35" s="6">
-        <v>21</v>
-      </c>
-      <c r="R35" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="6">
         <v>7006</v>
       </c>
@@ -5297,36 +6614,69 @@
       <c r="I36" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J36" s="6">
-        <v>500</v>
-      </c>
-      <c r="K36" s="6">
-        <v>100</v>
-      </c>
-      <c r="L36" s="6">
-        <v>100</v>
-      </c>
-      <c r="M36" s="6">
+      <c r="J36" s="6" cm="1">
+        <f t="array" ref="J36">_xlfn.SWITCH(O36,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R36-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R36-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R36-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R36-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R36-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K36" s="6" cm="1">
+        <f t="array" ref="K36">_xlfn.SWITCH(O36,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R36-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R36-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R36-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R36-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R36-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L36" s="6" cm="1">
+        <f t="array" ref="L36">_xlfn.SWITCH(O36,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R36-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R36-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R36-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R36-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R36-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M36" s="6" cm="1">
+        <f t="array" ref="M36">_xlfn.SWITCH(O36,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R36-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R36-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R36-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R36-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R36-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N36" s="6" cm="1">
+        <f t="array" ref="N36">_xlfn.SWITCH(O36,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R36-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R36-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R36-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R36-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R36-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R36" s="6">
+        <v>21</v>
+      </c>
+      <c r="S36" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N36" s="6">
-        <v>70</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P36" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q36" s="6">
-        <v>21</v>
-      </c>
-      <c r="R36" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="6">
         <v>7007</v>
       </c>
@@ -5354,36 +6704,69 @@
       <c r="I37" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J37" s="6">
-        <v>500</v>
-      </c>
-      <c r="K37" s="6">
-        <v>100</v>
-      </c>
-      <c r="L37" s="6">
-        <v>100</v>
-      </c>
-      <c r="M37" s="6">
+      <c r="J37" s="6" cm="1">
+        <f t="array" ref="J37">_xlfn.SWITCH(O37,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R37-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R37-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R37-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R37-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R37-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K37" s="6" cm="1">
+        <f t="array" ref="K37">_xlfn.SWITCH(O37,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R37-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R37-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R37-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R37-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R37-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L37" s="6" cm="1">
+        <f t="array" ref="L37">_xlfn.SWITCH(O37,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R37-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R37-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R37-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R37-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R37-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M37" s="6" cm="1">
+        <f t="array" ref="M37">_xlfn.SWITCH(O37,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R37-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R37-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R37-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R37-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R37-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N37" s="6" cm="1">
+        <f t="array" ref="N37">_xlfn.SWITCH(O37,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R37-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R37-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R37-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R37-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R37-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q37" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R37" s="6">
+        <v>21</v>
+      </c>
+      <c r="S37" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N37" s="6">
-        <v>70</v>
-      </c>
-      <c r="O37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P37" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q37" s="6">
-        <v>21</v>
-      </c>
-      <c r="R37" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="6">
         <v>7008</v>
       </c>
@@ -5411,36 +6794,69 @@
       <c r="I38" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J38" s="6">
-        <v>500</v>
-      </c>
-      <c r="K38" s="6">
-        <v>100</v>
-      </c>
-      <c r="L38" s="6">
-        <v>100</v>
-      </c>
-      <c r="M38" s="6">
+      <c r="J38" s="6" cm="1">
+        <f t="array" ref="J38">_xlfn.SWITCH(O38,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R38-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R38-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R38-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R38-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R38-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K38" s="6" cm="1">
+        <f t="array" ref="K38">_xlfn.SWITCH(O38,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R38-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R38-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R38-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R38-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R38-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L38" s="6" cm="1">
+        <f t="array" ref="L38">_xlfn.SWITCH(O38,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R38-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R38-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R38-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R38-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R38-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M38" s="6" cm="1">
+        <f t="array" ref="M38">_xlfn.SWITCH(O38,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R38-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R38-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R38-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R38-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R38-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N38" s="6" cm="1">
+        <f t="array" ref="N38">_xlfn.SWITCH(O38,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R38-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R38-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R38-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R38-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R38-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q38" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R38" s="6">
+        <v>21</v>
+      </c>
+      <c r="S38" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N38" s="6">
-        <v>70</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P38" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q38" s="6">
-        <v>21</v>
-      </c>
-      <c r="R38" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="6">
         <v>7009</v>
       </c>
@@ -5468,36 +6884,69 @@
       <c r="I39" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J39" s="6">
-        <v>500</v>
-      </c>
-      <c r="K39" s="6">
-        <v>100</v>
-      </c>
-      <c r="L39" s="6">
-        <v>100</v>
-      </c>
-      <c r="M39" s="6">
+      <c r="J39" s="6" cm="1">
+        <f t="array" ref="J39">_xlfn.SWITCH(O39,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R39-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R39-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R39-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R39-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R39-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K39" s="6" cm="1">
+        <f t="array" ref="K39">_xlfn.SWITCH(O39,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R39-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R39-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R39-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R39-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R39-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L39" s="6" cm="1">
+        <f t="array" ref="L39">_xlfn.SWITCH(O39,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R39-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R39-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R39-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R39-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R39-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M39" s="6" cm="1">
+        <f t="array" ref="M39">_xlfn.SWITCH(O39,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R39-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R39-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R39-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R39-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R39-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N39" s="6" cm="1">
+        <f t="array" ref="N39">_xlfn.SWITCH(O39,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R39-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R39-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R39-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R39-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R39-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R39" s="6">
+        <v>21</v>
+      </c>
+      <c r="S39" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N39" s="6">
-        <v>70</v>
-      </c>
-      <c r="O39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P39" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q39" s="6">
-        <v>21</v>
-      </c>
-      <c r="R39" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="6">
         <v>7010</v>
       </c>
@@ -5525,36 +6974,69 @@
       <c r="I40" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J40" s="6">
-        <v>500</v>
-      </c>
-      <c r="K40" s="6">
-        <v>100</v>
-      </c>
-      <c r="L40" s="6">
-        <v>100</v>
-      </c>
-      <c r="M40" s="6">
+      <c r="J40" s="6" cm="1">
+        <f t="array" ref="J40">_xlfn.SWITCH(O40,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R40-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R40-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R40-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R40-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R40-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K40" s="6" cm="1">
+        <f t="array" ref="K40">_xlfn.SWITCH(O40,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R40-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R40-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R40-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R40-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R40-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L40" s="6" cm="1">
+        <f t="array" ref="L40">_xlfn.SWITCH(O40,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R40-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R40-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R40-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R40-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R40-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M40" s="6" cm="1">
+        <f t="array" ref="M40">_xlfn.SWITCH(O40,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R40-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R40-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R40-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R40-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R40-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N40" s="6" cm="1">
+        <f t="array" ref="N40">_xlfn.SWITCH(O40,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R40-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R40-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R40-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R40-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R40-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R40" s="6">
+        <v>21</v>
+      </c>
+      <c r="S40" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N40" s="6">
-        <v>70</v>
-      </c>
-      <c r="O40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P40" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q40" s="6">
-        <v>21</v>
-      </c>
-      <c r="R40" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="6">
         <v>7011</v>
       </c>
@@ -5582,36 +7064,69 @@
       <c r="I41" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="J41" s="6">
-        <v>500</v>
-      </c>
-      <c r="K41" s="6">
-        <v>100</v>
-      </c>
-      <c r="L41" s="6">
-        <v>100</v>
-      </c>
-      <c r="M41" s="6">
+      <c r="J41" s="6" cm="1">
+        <f t="array" ref="J41">_xlfn.SWITCH(O41,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R41-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R41-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R41-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R41-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R41-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K41" s="6" cm="1">
+        <f t="array" ref="K41">_xlfn.SWITCH(O41,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R41-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R41-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R41-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R41-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R41-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L41" s="6" cm="1">
+        <f t="array" ref="L41">_xlfn.SWITCH(O41,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R41-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R41-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R41-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R41-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R41-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M41" s="6" cm="1">
+        <f t="array" ref="M41">_xlfn.SWITCH(O41,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R41-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R41-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R41-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R41-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R41-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N41" s="6" cm="1">
+        <f t="array" ref="N41">_xlfn.SWITCH(O41,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R41-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R41-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R41-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R41-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R41-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q41" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R41" s="6">
+        <v>21</v>
+      </c>
+      <c r="S41" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N41" s="6">
-        <v>70</v>
-      </c>
-      <c r="O41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P41" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q41" s="6">
-        <v>21</v>
-      </c>
-      <c r="R41" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="6">
         <v>7012</v>
       </c>
@@ -5639,36 +7154,69 @@
       <c r="I42" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J42" s="6">
-        <v>500</v>
-      </c>
-      <c r="K42" s="6">
-        <v>100</v>
-      </c>
-      <c r="L42" s="6">
-        <v>100</v>
-      </c>
-      <c r="M42" s="6">
+      <c r="J42" s="6" cm="1">
+        <f t="array" ref="J42">_xlfn.SWITCH(O42,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R42-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R42-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R42-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R42-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R42-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K42" s="6" cm="1">
+        <f t="array" ref="K42">_xlfn.SWITCH(O42,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R42-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R42-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R42-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R42-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R42-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L42" s="6" cm="1">
+        <f t="array" ref="L42">_xlfn.SWITCH(O42,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R42-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R42-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R42-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R42-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R42-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M42" s="6" cm="1">
+        <f t="array" ref="M42">_xlfn.SWITCH(O42,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R42-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R42-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R42-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R42-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R42-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N42" s="6" cm="1">
+        <f t="array" ref="N42">_xlfn.SWITCH(O42,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R42-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R42-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R42-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R42-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R42-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R42" s="6">
+        <v>21</v>
+      </c>
+      <c r="S42" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N42" s="6">
-        <v>70</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P42" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q42" s="6">
-        <v>21</v>
-      </c>
-      <c r="R42" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="6">
         <v>7013</v>
       </c>
@@ -5696,36 +7244,69 @@
       <c r="I43" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J43" s="6">
-        <v>500</v>
-      </c>
-      <c r="K43" s="6">
-        <v>100</v>
-      </c>
-      <c r="L43" s="6">
-        <v>100</v>
-      </c>
-      <c r="M43" s="6">
+      <c r="J43" s="6" cm="1">
+        <f t="array" ref="J43">_xlfn.SWITCH(O43,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R43-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R43-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R43-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R43-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R43-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K43" s="6" cm="1">
+        <f t="array" ref="K43">_xlfn.SWITCH(O43,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R43-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R43-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R43-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R43-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R43-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L43" s="6" cm="1">
+        <f t="array" ref="L43">_xlfn.SWITCH(O43,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R43-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R43-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R43-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R43-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R43-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M43" s="6" cm="1">
+        <f t="array" ref="M43">_xlfn.SWITCH(O43,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R43-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R43-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R43-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R43-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R43-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N43" s="6" cm="1">
+        <f t="array" ref="N43">_xlfn.SWITCH(O43,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R43-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R43-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R43-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R43-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R43-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R43" s="6">
+        <v>21</v>
+      </c>
+      <c r="S43" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N43" s="6">
-        <v>70</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P43" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q43" s="6">
-        <v>21</v>
-      </c>
-      <c r="R43" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="6">
         <v>7014</v>
       </c>
@@ -5753,36 +7334,69 @@
       <c r="I44" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="J44" s="6">
-        <v>500</v>
-      </c>
-      <c r="K44" s="6">
-        <v>100</v>
-      </c>
-      <c r="L44" s="6">
-        <v>100</v>
-      </c>
-      <c r="M44" s="6">
+      <c r="J44" s="6" cm="1">
+        <f t="array" ref="J44">_xlfn.SWITCH(O44,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R44-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R44-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R44-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R44-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R44-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K44" s="6" cm="1">
+        <f t="array" ref="K44">_xlfn.SWITCH(O44,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R44-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R44-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R44-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R44-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R44-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L44" s="6" cm="1">
+        <f t="array" ref="L44">_xlfn.SWITCH(O44,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R44-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R44-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R44-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R44-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R44-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M44" s="6" cm="1">
+        <f t="array" ref="M44">_xlfn.SWITCH(O44,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R44-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R44-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R44-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R44-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R44-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N44" s="6" cm="1">
+        <f t="array" ref="N44">_xlfn.SWITCH(O44,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R44-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R44-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R44-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R44-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R44-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q44" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R44" s="6">
+        <v>21</v>
+      </c>
+      <c r="S44" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N44" s="6">
-        <v>70</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P44" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q44" s="6">
-        <v>21</v>
-      </c>
-      <c r="R44" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="6">
         <v>7015</v>
       </c>
@@ -5810,36 +7424,69 @@
       <c r="I45" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J45" s="6">
-        <v>500</v>
-      </c>
-      <c r="K45" s="6">
-        <v>100</v>
-      </c>
-      <c r="L45" s="6">
-        <v>100</v>
-      </c>
-      <c r="M45" s="6">
+      <c r="J45" s="6" cm="1">
+        <f t="array" ref="J45">_xlfn.SWITCH(O45,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R45-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R45-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R45-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R45-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R45-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K45" s="6" cm="1">
+        <f t="array" ref="K45">_xlfn.SWITCH(O45,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R45-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R45-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R45-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R45-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R45-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L45" s="6" cm="1">
+        <f t="array" ref="L45">_xlfn.SWITCH(O45,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R45-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R45-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R45-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R45-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R45-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M45" s="6" cm="1">
+        <f t="array" ref="M45">_xlfn.SWITCH(O45,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R45-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R45-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R45-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R45-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R45-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N45" s="6" cm="1">
+        <f t="array" ref="N45">_xlfn.SWITCH(O45,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R45-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R45-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R45-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R45-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R45-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q45" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R45" s="6">
+        <v>21</v>
+      </c>
+      <c r="S45" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N45" s="6">
-        <v>70</v>
-      </c>
-      <c r="O45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P45" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q45" s="6">
-        <v>21</v>
-      </c>
-      <c r="R45" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="6">
         <v>7016</v>
       </c>
@@ -5867,36 +7514,69 @@
       <c r="I46" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="J46" s="6">
-        <v>500</v>
-      </c>
-      <c r="K46" s="6">
-        <v>100</v>
-      </c>
-      <c r="L46" s="6">
-        <v>100</v>
-      </c>
-      <c r="M46" s="6">
+      <c r="J46" s="6" cm="1">
+        <f t="array" ref="J46">_xlfn.SWITCH(O46,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R46-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R46-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R46-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R46-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R46-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K46" s="6" cm="1">
+        <f t="array" ref="K46">_xlfn.SWITCH(O46,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R46-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R46-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R46-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R46-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R46-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L46" s="6" cm="1">
+        <f t="array" ref="L46">_xlfn.SWITCH(O46,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R46-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R46-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R46-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R46-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R46-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M46" s="6" cm="1">
+        <f t="array" ref="M46">_xlfn.SWITCH(O46,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R46-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R46-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R46-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R46-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R46-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N46" s="6" cm="1">
+        <f t="array" ref="N46">_xlfn.SWITCH(O46,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R46-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R46-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R46-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R46-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R46-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R46" s="6">
+        <v>21</v>
+      </c>
+      <c r="S46" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="N46" s="6">
-        <v>70</v>
-      </c>
-      <c r="O46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P46" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q46" s="6">
-        <v>21</v>
-      </c>
-      <c r="R46" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="6">
         <v>7017</v>
       </c>
@@ -5924,33 +7604,66 @@
       <c r="I47" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J47" s="6">
-        <v>500</v>
-      </c>
-      <c r="K47" s="6">
-        <v>100</v>
-      </c>
-      <c r="L47" s="6">
-        <v>100</v>
-      </c>
-      <c r="M47" s="6">
+      <c r="J47" s="6" cm="1">
+        <f t="array" ref="J47">_xlfn.SWITCH(O47,
+"Balance",150+GrowthType!$B$2*(EnemyStatus!R47-1),
+"Atype",150+GrowthType!$B$3*(EnemyStatus!R47-1),
+"Dtype",150+GrowthType!$B$4*(EnemyStatus!R47-1),
+"Itype",150+GrowthType!$B$5*(EnemyStatus!R47-1),
+"Stype",150+GrowthType!$B$6*(EnemyStatus!R47-1))</f>
+        <v>450</v>
+      </c>
+      <c r="K47" s="6" cm="1">
+        <f t="array" ref="K47">_xlfn.SWITCH(O47,
+ "Balance", 30+GrowthType!$C$2*(EnemyStatus!R47-1),
+ "Atype",   30+GrowthType!$C$3*(EnemyStatus!R47-1),
+ "Dtype",   30+GrowthType!$C$4*(EnemyStatus!R47-1),
+ "Itype",   30+GrowthType!$C$5*(EnemyStatus!R47-1),
+ "Stype",   30+GrowthType!$C$6*(EnemyStatus!R47-1))</f>
+        <v>90</v>
+      </c>
+      <c r="L47" s="6" cm="1">
+        <f t="array" ref="L47">_xlfn.SWITCH(O47,
+ "Balance", 30+GrowthType!$D$2*(EnemyStatus!R47-1),
+ "Atype",   30+GrowthType!$D$3*(EnemyStatus!R47-1),
+ "Dtype",   30+GrowthType!$D$4*(EnemyStatus!R47-1),
+ "Itype",   30+GrowthType!$D$5*(EnemyStatus!R47-1),
+ "Stype",   30+GrowthType!$D$6*(EnemyStatus!R47-1))</f>
+        <v>90</v>
+      </c>
+      <c r="M47" s="6" cm="1">
+        <f t="array" ref="M47">_xlfn.SWITCH(O47,
+ "Balance", 20+GrowthType!$E$2*(EnemyStatus!R47-1),
+ "Atype",   20+GrowthType!$E$3*(EnemyStatus!R47-1),
+ "Dtype",   20+GrowthType!$E$4*(EnemyStatus!R47-1),
+ "Itype",   20+GrowthType!$E$5*(EnemyStatus!R47-1),
+ "Stype",   20+GrowthType!$E$6*(EnemyStatus!R47-1))</f>
+        <v>60</v>
+      </c>
+      <c r="N47" s="6" cm="1">
+        <f t="array" ref="N47">_xlfn.SWITCH(O47,
+ "Balance", 20+GrowthType!$F$2*(EnemyStatus!R47-1),
+ "Atype",   20+GrowthType!$F$3*(EnemyStatus!R47-1),
+ "Dtype",   20+GrowthType!$F$4*(EnemyStatus!R47-1),
+ "Itype",   20+GrowthType!$F$5*(EnemyStatus!R47-1),
+ "Stype",   20+GrowthType!$F$6*(EnemyStatus!R47-1))</f>
+        <v>60</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>-1</v>
+      </c>
+      <c r="R47" s="6">
+        <v>21</v>
+      </c>
+      <c r="S47" s="6">
+        <f t="shared" si="2"/>
         <v>70</v>
-      </c>
-      <c r="N47" s="6">
-        <v>70</v>
-      </c>
-      <c r="O47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="P47" s="6">
-        <v>-1</v>
-      </c>
-      <c r="Q47" s="6">
-        <v>21</v>
-      </c>
-      <c r="R47" s="6">
-        <f t="shared" si="1"/>
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -6099,6 +7812,265 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54DD1810-2366-44EC-B9BE-BD69FF5162E9}">
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>1200</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B63A90-5912-4059-8F6A-B0CD3C2852FE}">
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -6632,7 +8604,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68A09D80-B6F8-4637-B17F-FF997CFB0BAB}">
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -7587,7 +9559,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0F4277A-D612-42DD-BD41-F36E114C3D17}">
   <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
@@ -8359,7 +10331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E24E6DA1-6182-4200-AD23-D3557DB026A8}">
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
